--- a/AutosurveillanceTemplates/PREL.xlsx
+++ b/AutosurveillanceTemplates/PREL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD2F354-0C1F-45FE-B9EF-00AC453F521A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C79A2F-DCCB-41FC-B861-38AAE9FDA241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prel" sheetId="49" r:id="rId1"/>
@@ -30,12 +30,13 @@
     <definedName name="LISTE_1">PARAM!$A$21:$A$23</definedName>
     <definedName name="LISTE_2">PARAM!$B$21:$B$24</definedName>
     <definedName name="LISTE_3">PARAM!$C$21:$C$25</definedName>
-    <definedName name="LISTE_4">PARAM!$D$21:$D$27</definedName>
+    <definedName name="LISTE_4">PARAM!$D$21:$D$25</definedName>
     <definedName name="LISTE_5">PARAM!$F$21:$F$25</definedName>
-    <definedName name="LISTE_6">PARAM!$G1048575</definedName>
+    <definedName name="LISTE_6">PARAM!$G1</definedName>
+    <definedName name="LISTE_7">PARAM!$H$21:$H$23</definedName>
     <definedName name="Montage_sonde">PARAM!$G$44:$G$47</definedName>
-    <definedName name="Q_en_charge">PARAM!$A$3:$A$30</definedName>
-    <definedName name="Q_Gravitaire">PARAM!$B$30:$B$39</definedName>
+    <definedName name="Q_en_charge">PARAM!$A$30:$A$34</definedName>
+    <definedName name="Q_Gravitaire">PARAM!$B$30:$B$38</definedName>
     <definedName name="Satisfaction">PARAM!$D$44:$D$46</definedName>
     <definedName name="Type_capteur">PARAM!$C$44:$C$48</definedName>
     <definedName name="Type_equipement">PARAM!$C$4:$C$6</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="349">
   <si>
     <t>Code</t>
   </si>
@@ -1926,6 +1927,15 @@
   </si>
   <si>
     <t>Autres équipements</t>
+  </si>
+  <si>
+    <t>LISTE_7</t>
+  </si>
+  <si>
+    <t>Entre 10 et 20%</t>
+  </si>
+  <si>
+    <t>Non validé (&gt;20%)</t>
   </si>
 </sst>
 </file>
@@ -2383,7 +2393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="105">
+  <borders count="104">
     <border>
       <left/>
       <right/>
@@ -3660,19 +3670,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -3721,7 +3718,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4211,9 +4208,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4237,15 +4231,15 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="101" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="102" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="103" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="104" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4291,9 +4285,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="100" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4303,8 +4294,268 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="101" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="166" fontId="31" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="26" fillId="13" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="13" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="13" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="13" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4344,283 +4595,23 @@
     <xf numFmtId="0" fontId="33" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="26" fillId="13" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="26" fillId="13" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="13" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="13" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5216,9 +5207,9 @@
     <col min="11" max="12" width="11.703125" style="80" customWidth="1"/>
     <col min="13" max="18" width="10.703125" style="80"/>
     <col min="19" max="19" width="2.703125" style="80" customWidth="1"/>
-    <col min="20" max="20" width="2.703125" style="293" customWidth="1"/>
-    <col min="21" max="26" width="10.703125" style="293"/>
-    <col min="27" max="30" width="10.703125" style="294"/>
+    <col min="20" max="20" width="2.703125" style="196" customWidth="1"/>
+    <col min="21" max="26" width="10.703125" style="196"/>
+    <col min="27" max="30" width="10.703125" style="197"/>
     <col min="31" max="16384" width="10.703125" style="80"/>
   </cols>
   <sheetData>
@@ -5244,131 +5235,131 @@
     </row>
     <row r="2" spans="2:21" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="66"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="267" t="s">
         <v>282</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="223"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
-      <c r="M2" s="223"/>
-      <c r="N2" s="223"/>
-      <c r="O2" s="223"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="224"/>
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="268"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="268"/>
+      <c r="Q2" s="268"/>
+      <c r="R2" s="269"/>
       <c r="S2" s="67"/>
     </row>
     <row r="3" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="78"/>
-      <c r="C3" s="225" t="s">
+      <c r="C3" s="262" t="s">
         <v>247</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="227"/>
-      <c r="G3" s="227"/>
-      <c r="H3" s="226" t="s">
+      <c r="D3" s="263"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="263" t="s">
         <v>242</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="227"/>
-      <c r="K3" s="227"/>
-      <c r="L3" s="227"/>
-      <c r="M3" s="226" t="s">
+      <c r="I3" s="263"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="263" t="s">
         <v>244</v>
       </c>
-      <c r="N3" s="226"/>
-      <c r="O3" s="226"/>
-      <c r="P3" s="228"/>
-      <c r="Q3" s="228"/>
-      <c r="R3" s="229"/>
+      <c r="N3" s="263"/>
+      <c r="O3" s="263"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="266"/>
       <c r="S3" s="79"/>
     </row>
     <row r="4" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="78"/>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="262" t="s">
         <v>239</v>
       </c>
-      <c r="D4" s="226"/>
-      <c r="E4" s="227"/>
-      <c r="F4" s="227"/>
-      <c r="G4" s="227"/>
-      <c r="H4" s="226" t="s">
+      <c r="D4" s="263"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="263" t="s">
         <v>249</v>
       </c>
-      <c r="I4" s="226"/>
-      <c r="J4" s="227"/>
-      <c r="K4" s="227"/>
-      <c r="L4" s="227"/>
-      <c r="M4" s="226" t="s">
+      <c r="I4" s="263"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="263" t="s">
         <v>245</v>
       </c>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="229"/>
+      <c r="N4" s="263"/>
+      <c r="O4" s="263"/>
+      <c r="P4" s="265"/>
+      <c r="Q4" s="265"/>
+      <c r="R4" s="266"/>
       <c r="S4" s="79"/>
     </row>
     <row r="5" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="78"/>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="262" t="s">
         <v>240</v>
       </c>
-      <c r="D5" s="226"/>
-      <c r="E5" s="227"/>
-      <c r="F5" s="227"/>
-      <c r="G5" s="227"/>
-      <c r="H5" s="226" t="s">
+      <c r="D5" s="263"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="263" t="s">
         <v>248</v>
       </c>
-      <c r="I5" s="226"/>
-      <c r="J5" s="227"/>
-      <c r="K5" s="227"/>
-      <c r="L5" s="227"/>
-      <c r="M5" s="226" t="s">
+      <c r="I5" s="263"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="M5" s="263" t="s">
         <v>246</v>
       </c>
-      <c r="N5" s="226"/>
-      <c r="O5" s="226"/>
-      <c r="P5" s="239"/>
-      <c r="Q5" s="239"/>
-      <c r="R5" s="240"/>
+      <c r="N5" s="263"/>
+      <c r="O5" s="263"/>
+      <c r="P5" s="273"/>
+      <c r="Q5" s="273"/>
+      <c r="R5" s="274"/>
       <c r="S5" s="79"/>
     </row>
     <row r="6" spans="2:21" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="78"/>
-      <c r="C6" s="251" t="s">
+      <c r="C6" s="239" t="s">
         <v>241</v>
       </c>
-      <c r="D6" s="252"/>
-      <c r="E6" s="253"/>
-      <c r="F6" s="253"/>
-      <c r="G6" s="253"/>
-      <c r="H6" s="252" t="s">
+      <c r="D6" s="240"/>
+      <c r="E6" s="241"/>
+      <c r="F6" s="241"/>
+      <c r="G6" s="241"/>
+      <c r="H6" s="240" t="s">
         <v>243</v>
       </c>
-      <c r="I6" s="252"/>
-      <c r="J6" s="253">
+      <c r="I6" s="240"/>
+      <c r="J6" s="241" t="str">
         <f>D37</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="253"/>
-      <c r="L6" s="253"/>
-      <c r="M6" s="252" t="s">
+        <v>Vanne de prélèvement asservie</v>
+      </c>
+      <c r="K6" s="241"/>
+      <c r="L6" s="241"/>
+      <c r="M6" s="240" t="s">
         <v>250</v>
       </c>
-      <c r="N6" s="252"/>
-      <c r="O6" s="252"/>
-      <c r="P6" s="254"/>
-      <c r="Q6" s="254"/>
-      <c r="R6" s="255"/>
+      <c r="N6" s="240"/>
+      <c r="O6" s="240"/>
+      <c r="P6" s="242"/>
+      <c r="Q6" s="242"/>
+      <c r="R6" s="243"/>
       <c r="S6" s="79"/>
     </row>
     <row r="7" spans="2:21" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -5393,24 +5384,24 @@
     </row>
     <row r="8" spans="2:21" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="68"/>
-      <c r="C8" s="241" t="s">
+      <c r="C8" s="214" t="s">
         <v>260</v>
       </c>
-      <c r="D8" s="242"/>
-      <c r="E8" s="242"/>
-      <c r="F8" s="242"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="242"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="242"/>
-      <c r="K8" s="242"/>
-      <c r="L8" s="242"/>
-      <c r="M8" s="242"/>
-      <c r="N8" s="242"/>
-      <c r="O8" s="242"/>
-      <c r="P8" s="242"/>
-      <c r="Q8" s="242"/>
-      <c r="R8" s="243"/>
+      <c r="D8" s="215"/>
+      <c r="E8" s="215"/>
+      <c r="F8" s="215"/>
+      <c r="G8" s="215"/>
+      <c r="H8" s="215"/>
+      <c r="I8" s="215"/>
+      <c r="J8" s="215"/>
+      <c r="K8" s="215"/>
+      <c r="L8" s="215"/>
+      <c r="M8" s="215"/>
+      <c r="N8" s="215"/>
+      <c r="O8" s="215"/>
+      <c r="P8" s="215"/>
+      <c r="Q8" s="215"/>
+      <c r="R8" s="216"/>
       <c r="S8" s="70"/>
     </row>
     <row r="9" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5436,119 +5427,119 @@
     <row r="10" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="69"/>
       <c r="C10" s="94"/>
-      <c r="D10" s="218" t="s">
+      <c r="D10" s="221" t="s">
         <v>200</v>
       </c>
-      <c r="E10" s="219"/>
-      <c r="F10" s="219"/>
-      <c r="G10" s="219"/>
-      <c r="H10" s="219"/>
-      <c r="I10" s="219"/>
-      <c r="J10" s="219"/>
-      <c r="K10" s="219"/>
-      <c r="L10" s="219"/>
-      <c r="M10" s="219"/>
-      <c r="N10" s="219"/>
-      <c r="O10" s="219"/>
-      <c r="P10" s="219"/>
-      <c r="Q10" s="256"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="222"/>
+      <c r="H10" s="222"/>
+      <c r="I10" s="222"/>
+      <c r="J10" s="222"/>
+      <c r="K10" s="222"/>
+      <c r="L10" s="222"/>
+      <c r="M10" s="222"/>
+      <c r="N10" s="222"/>
+      <c r="O10" s="222"/>
+      <c r="P10" s="222"/>
+      <c r="Q10" s="244"/>
       <c r="R10" s="95"/>
       <c r="S10" s="71"/>
     </row>
     <row r="11" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="69"/>
       <c r="C11" s="94"/>
-      <c r="D11" s="233" t="s">
+      <c r="D11" s="245" t="s">
         <v>263</v>
       </c>
-      <c r="E11" s="234"/>
-      <c r="F11" s="235"/>
-      <c r="G11" s="230"/>
-      <c r="H11" s="231"/>
-      <c r="I11" s="231"/>
-      <c r="J11" s="231"/>
-      <c r="K11" s="231"/>
-      <c r="L11" s="231"/>
-      <c r="M11" s="231"/>
-      <c r="N11" s="231"/>
-      <c r="O11" s="231"/>
-      <c r="P11" s="231"/>
-      <c r="Q11" s="232"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="247"/>
+      <c r="G11" s="270"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="271"/>
+      <c r="M11" s="271"/>
+      <c r="N11" s="271"/>
+      <c r="O11" s="271"/>
+      <c r="P11" s="271"/>
+      <c r="Q11" s="272"/>
       <c r="R11" s="95"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="69"/>
       <c r="C12" s="94"/>
-      <c r="D12" s="233" t="s">
+      <c r="D12" s="245" t="s">
         <v>251</v>
       </c>
-      <c r="E12" s="234"/>
-      <c r="F12" s="235"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="237"/>
-      <c r="I12" s="237"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="233" t="s">
+      <c r="E12" s="246"/>
+      <c r="F12" s="247"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="249"/>
+      <c r="I12" s="249"/>
+      <c r="J12" s="250"/>
+      <c r="K12" s="245" t="s">
         <v>202</v>
       </c>
-      <c r="L12" s="234"/>
-      <c r="M12" s="235"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="237"/>
-      <c r="P12" s="237"/>
-      <c r="Q12" s="238"/>
+      <c r="L12" s="246"/>
+      <c r="M12" s="247"/>
+      <c r="N12" s="248"/>
+      <c r="O12" s="249"/>
+      <c r="P12" s="249"/>
+      <c r="Q12" s="250"/>
       <c r="R12" s="95"/>
       <c r="S12" s="71"/>
     </row>
     <row r="13" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="69"/>
       <c r="C13" s="94"/>
-      <c r="D13" s="233" t="s">
+      <c r="D13" s="245" t="s">
         <v>201</v>
       </c>
-      <c r="E13" s="234"/>
-      <c r="F13" s="235"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="237"/>
-      <c r="I13" s="237"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="233" t="s">
+      <c r="E13" s="246"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="249"/>
+      <c r="J13" s="250"/>
+      <c r="K13" s="245" t="s">
         <v>264</v>
       </c>
-      <c r="L13" s="234"/>
-      <c r="M13" s="235"/>
-      <c r="N13" s="236"/>
-      <c r="O13" s="237"/>
-      <c r="P13" s="237"/>
-      <c r="Q13" s="238"/>
+      <c r="L13" s="246"/>
+      <c r="M13" s="247"/>
+      <c r="N13" s="248"/>
+      <c r="O13" s="249"/>
+      <c r="P13" s="249"/>
+      <c r="Q13" s="250"/>
       <c r="R13" s="95"/>
       <c r="S13" s="71"/>
     </row>
     <row r="14" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B14" s="69"/>
       <c r="C14" s="94"/>
-      <c r="D14" s="233" t="s">
+      <c r="D14" s="245" t="s">
         <v>252</v>
       </c>
-      <c r="E14" s="234"/>
-      <c r="F14" s="235"/>
-      <c r="G14" s="236"/>
-      <c r="H14" s="237"/>
-      <c r="I14" s="237"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="233" t="s">
+      <c r="E14" s="246"/>
+      <c r="F14" s="247"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="250"/>
+      <c r="K14" s="245" t="s">
         <v>203</v>
       </c>
-      <c r="L14" s="234"/>
-      <c r="M14" s="235"/>
-      <c r="N14" s="236"/>
-      <c r="O14" s="237"/>
-      <c r="P14" s="237"/>
-      <c r="Q14" s="238"/>
+      <c r="L14" s="246"/>
+      <c r="M14" s="247"/>
+      <c r="N14" s="248"/>
+      <c r="O14" s="249"/>
+      <c r="P14" s="249"/>
+      <c r="Q14" s="250"/>
       <c r="R14" s="95"/>
       <c r="S14" s="71"/>
-      <c r="U14" s="293" t="str">
+      <c r="U14" s="196" t="str">
         <f>IF(N14&lt;&gt;"",IF(N14&gt;=9,"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -5556,24 +5547,24 @@
     <row r="15" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B15" s="69"/>
       <c r="C15" s="94"/>
-      <c r="D15" s="233" t="s">
+      <c r="D15" s="245" t="s">
         <v>253</v>
       </c>
-      <c r="E15" s="234"/>
-      <c r="F15" s="235"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="237"/>
-      <c r="I15" s="237"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="233" t="s">
+      <c r="E15" s="246"/>
+      <c r="F15" s="247"/>
+      <c r="G15" s="248"/>
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="250"/>
+      <c r="K15" s="245" t="s">
         <v>254</v>
       </c>
-      <c r="L15" s="234"/>
-      <c r="M15" s="235"/>
-      <c r="N15" s="236"/>
-      <c r="O15" s="237"/>
-      <c r="P15" s="237"/>
-      <c r="Q15" s="238"/>
+      <c r="L15" s="246"/>
+      <c r="M15" s="247"/>
+      <c r="N15" s="248"/>
+      <c r="O15" s="249"/>
+      <c r="P15" s="249"/>
+      <c r="Q15" s="250"/>
       <c r="R15" s="95"/>
       <c r="S15" s="71"/>
     </row>
@@ -5600,18 +5591,18 @@
     <row r="17" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B17" s="69"/>
       <c r="C17" s="94"/>
-      <c r="D17" s="218" t="s">
+      <c r="D17" s="221" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="219"/>
-      <c r="F17" s="219"/>
-      <c r="G17" s="219"/>
-      <c r="H17" s="219"/>
-      <c r="I17" s="219"/>
-      <c r="J17" s="219"/>
-      <c r="K17" s="219"/>
-      <c r="L17" s="219"/>
-      <c r="M17" s="219"/>
+      <c r="E17" s="222"/>
+      <c r="F17" s="222"/>
+      <c r="G17" s="222"/>
+      <c r="H17" s="222"/>
+      <c r="I17" s="222"/>
+      <c r="J17" s="222"/>
+      <c r="K17" s="222"/>
+      <c r="L17" s="222"/>
+      <c r="M17" s="222"/>
       <c r="N17" s="76"/>
       <c r="O17" s="77"/>
       <c r="P17" s="77"/>
@@ -5622,10 +5613,10 @@
     <row r="18" spans="2:22" ht="39.950000000000003" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B18" s="69"/>
       <c r="C18" s="94"/>
-      <c r="D18" s="261" t="s">
+      <c r="D18" s="255" t="s">
         <v>237</v>
       </c>
-      <c r="E18" s="262"/>
+      <c r="E18" s="256"/>
       <c r="F18" s="86" t="s">
         <v>205</v>
       </c>
@@ -5635,17 +5626,17 @@
       <c r="H18" s="88" t="s">
         <v>207</v>
       </c>
-      <c r="I18" s="263" t="s">
+      <c r="I18" s="257" t="s">
         <v>208</v>
       </c>
-      <c r="J18" s="264"/>
+      <c r="J18" s="258"/>
       <c r="K18" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="L18" s="263" t="s">
+      <c r="L18" s="257" t="s">
         <v>79</v>
       </c>
-      <c r="M18" s="265"/>
+      <c r="M18" s="259"/>
       <c r="N18" s="84"/>
       <c r="O18" s="84"/>
       <c r="P18" s="84"/>
@@ -5656,32 +5647,32 @@
     <row r="19" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="69"/>
       <c r="C19" s="94"/>
-      <c r="D19" s="201"/>
-      <c r="E19" s="202"/>
+      <c r="D19" s="277"/>
+      <c r="E19" s="278"/>
       <c r="F19" s="114"/>
       <c r="G19" s="115"/>
       <c r="H19" s="116"/>
-      <c r="I19" s="199" t="str">
+      <c r="I19" s="275" t="str">
         <f>IF(F19&lt;&gt;"",AVERAGE(F19:H19),"")</f>
         <v/>
       </c>
-      <c r="J19" s="200"/>
+      <c r="J19" s="276"/>
       <c r="K19" s="107" t="str">
         <f>IF(COUNTA(F19:H19)&gt;0,STDEVP(F19:H19),"")</f>
         <v/>
       </c>
-      <c r="L19" s="257" t="str">
+      <c r="L19" s="251" t="str">
         <f>IF(AND(I19&lt;&gt;0, K19&lt;&gt;"",I19&lt;&gt;""),K19/I19,"")</f>
         <v/>
       </c>
-      <c r="M19" s="258"/>
+      <c r="M19" s="252"/>
       <c r="N19" s="81"/>
       <c r="O19" s="81"/>
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
       <c r="R19" s="95"/>
       <c r="S19" s="71"/>
-      <c r="U19" s="293" t="str">
+      <c r="U19" s="196" t="str">
         <f>IF(I19&lt;&gt;"",IF(AND(I19&gt;=50,ABS(L19)&lt;=0.05),"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -5709,34 +5700,34 @@
     <row r="21" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B21" s="69"/>
       <c r="C21" s="94"/>
-      <c r="D21" s="218" t="s">
+      <c r="D21" s="221" t="s">
         <v>209</v>
       </c>
-      <c r="E21" s="219"/>
-      <c r="F21" s="219"/>
-      <c r="G21" s="219"/>
-      <c r="H21" s="219"/>
-      <c r="I21" s="271" t="s">
+      <c r="E21" s="222"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="222"/>
+      <c r="I21" s="223" t="s">
         <v>210</v>
       </c>
-      <c r="J21" s="272"/>
+      <c r="J21" s="224"/>
       <c r="K21" s="81"/>
-      <c r="L21" s="205" t="s">
+      <c r="L21" s="281" t="s">
         <v>214</v>
       </c>
-      <c r="M21" s="206"/>
-      <c r="N21" s="206"/>
-      <c r="O21" s="206"/>
-      <c r="P21" s="206"/>
-      <c r="Q21" s="207"/>
+      <c r="M21" s="282"/>
+      <c r="N21" s="282"/>
+      <c r="O21" s="282"/>
+      <c r="P21" s="282"/>
+      <c r="Q21" s="283"/>
       <c r="R21" s="95"/>
       <c r="S21" s="71"/>
     </row>
     <row r="22" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B22" s="69"/>
       <c r="C22" s="94"/>
-      <c r="D22" s="259"/>
-      <c r="E22" s="259"/>
+      <c r="D22" s="253"/>
+      <c r="E22" s="253"/>
       <c r="F22" s="89" t="s">
         <v>211</v>
       </c>
@@ -5746,45 +5737,45 @@
       <c r="H22" s="91" t="s">
         <v>213</v>
       </c>
-      <c r="I22" s="260" t="s">
+      <c r="I22" s="254" t="s">
         <v>80</v>
       </c>
-      <c r="J22" s="260"/>
+      <c r="J22" s="254"/>
       <c r="K22" s="81"/>
-      <c r="L22" s="208" t="s">
+      <c r="L22" s="284" t="s">
         <v>238</v>
       </c>
-      <c r="M22" s="209"/>
-      <c r="N22" s="209"/>
-      <c r="O22" s="209"/>
-      <c r="P22" s="209"/>
-      <c r="Q22" s="210"/>
+      <c r="M22" s="285"/>
+      <c r="N22" s="285"/>
+      <c r="O22" s="285"/>
+      <c r="P22" s="285"/>
+      <c r="Q22" s="286"/>
       <c r="R22" s="95"/>
       <c r="S22" s="71"/>
     </row>
     <row r="23" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B23" s="69"/>
       <c r="C23" s="94"/>
-      <c r="D23" s="266" t="s">
+      <c r="D23" s="229" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="266"/>
+      <c r="E23" s="229"/>
       <c r="F23" s="111"/>
       <c r="G23" s="117"/>
       <c r="H23" s="112"/>
-      <c r="I23" s="267" t="str">
+      <c r="I23" s="260" t="str">
         <f>IF(F23&gt;0,AVERAGE(F23:H23),"")</f>
         <v/>
       </c>
-      <c r="J23" s="268"/>
+      <c r="J23" s="261"/>
       <c r="K23" s="81"/>
-      <c r="L23" s="203" t="s">
+      <c r="L23" s="279" t="s">
         <v>256</v>
       </c>
-      <c r="M23" s="203"/>
-      <c r="N23" s="203"/>
-      <c r="O23" s="203"/>
-      <c r="P23" s="204"/>
+      <c r="M23" s="279"/>
+      <c r="N23" s="279"/>
+      <c r="O23" s="279"/>
+      <c r="P23" s="280"/>
       <c r="Q23" s="121"/>
       <c r="R23" s="95"/>
       <c r="S23" s="71"/>
@@ -5792,10 +5783,10 @@
     <row r="24" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B24" s="69"/>
       <c r="C24" s="94"/>
-      <c r="D24" s="266" t="s">
+      <c r="D24" s="229" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="266"/>
+      <c r="E24" s="229"/>
       <c r="F24" s="102" t="str">
         <f>IF(F23&gt;0,N13/F23,"")</f>
         <v/>
@@ -5808,23 +5799,23 @@
         <f>IF(H23&gt;0,N13/H23,"")</f>
         <v/>
       </c>
-      <c r="I24" s="274" t="str">
+      <c r="I24" s="230" t="str">
         <f>IF(F24&lt;&gt;"",AVERAGE(F24:H24),"")</f>
         <v/>
       </c>
-      <c r="J24" s="275"/>
+      <c r="J24" s="231"/>
       <c r="K24" s="81"/>
-      <c r="L24" s="203" t="s">
+      <c r="L24" s="279" t="s">
         <v>257</v>
       </c>
-      <c r="M24" s="203"/>
-      <c r="N24" s="203"/>
-      <c r="O24" s="203"/>
-      <c r="P24" s="204"/>
+      <c r="M24" s="279"/>
+      <c r="N24" s="279"/>
+      <c r="O24" s="279"/>
+      <c r="P24" s="280"/>
       <c r="Q24" s="121"/>
       <c r="R24" s="95"/>
       <c r="S24" s="71"/>
-      <c r="U24" s="293" t="str">
+      <c r="U24" s="196" t="str">
         <f>IF(I24&lt;&gt;"",IF(I24&gt;=0.5,"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -5840,13 +5831,13 @@
       <c r="I25" s="81"/>
       <c r="J25" s="81"/>
       <c r="K25" s="81"/>
-      <c r="L25" s="203" t="s">
+      <c r="L25" s="279" t="s">
         <v>258</v>
       </c>
-      <c r="M25" s="203"/>
-      <c r="N25" s="203"/>
-      <c r="O25" s="203"/>
-      <c r="P25" s="204"/>
+      <c r="M25" s="279"/>
+      <c r="N25" s="279"/>
+      <c r="O25" s="279"/>
+      <c r="P25" s="280"/>
       <c r="Q25" s="108" t="str">
         <f>IF(COUNTA(Q23:Q24)&gt;0,TRUNC(Q24/Q23,0),"")</f>
         <v/>
@@ -5857,23 +5848,23 @@
     <row r="26" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B26" s="69"/>
       <c r="C26" s="94"/>
-      <c r="D26" s="218" t="s">
+      <c r="D26" s="221" t="s">
         <v>216</v>
       </c>
-      <c r="E26" s="219"/>
-      <c r="F26" s="219"/>
-      <c r="G26" s="219"/>
-      <c r="H26" s="219"/>
-      <c r="I26" s="219"/>
+      <c r="E26" s="222"/>
+      <c r="F26" s="222"/>
+      <c r="G26" s="222"/>
+      <c r="H26" s="222"/>
+      <c r="I26" s="222"/>
       <c r="J26" s="76"/>
       <c r="K26" s="81"/>
-      <c r="L26" s="203" t="s">
+      <c r="L26" s="279" t="s">
         <v>259</v>
       </c>
-      <c r="M26" s="203"/>
-      <c r="N26" s="203"/>
-      <c r="O26" s="203"/>
-      <c r="P26" s="204"/>
+      <c r="M26" s="279"/>
+      <c r="N26" s="279"/>
+      <c r="O26" s="279"/>
+      <c r="P26" s="280"/>
       <c r="Q26" s="120"/>
       <c r="R26" s="95"/>
       <c r="S26" s="71"/>
@@ -5881,27 +5872,27 @@
     <row r="27" spans="2:22" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B27" s="69"/>
       <c r="C27" s="94"/>
-      <c r="D27" s="212" t="s">
+      <c r="D27" s="219" t="s">
         <v>217</v>
       </c>
-      <c r="E27" s="213"/>
-      <c r="F27" s="212" t="s">
+      <c r="E27" s="220"/>
+      <c r="F27" s="219" t="s">
         <v>218</v>
       </c>
-      <c r="G27" s="213"/>
-      <c r="H27" s="214" t="s">
+      <c r="G27" s="220"/>
+      <c r="H27" s="225" t="s">
         <v>219</v>
       </c>
-      <c r="I27" s="215"/>
+      <c r="I27" s="226"/>
       <c r="J27" s="81"/>
       <c r="K27" s="81"/>
-      <c r="L27" s="203" t="s">
+      <c r="L27" s="279" t="s">
         <v>255</v>
       </c>
-      <c r="M27" s="203"/>
-      <c r="N27" s="203"/>
-      <c r="O27" s="203"/>
-      <c r="P27" s="204"/>
+      <c r="M27" s="279"/>
+      <c r="N27" s="279"/>
+      <c r="O27" s="279"/>
+      <c r="P27" s="280"/>
       <c r="Q27" s="119"/>
       <c r="R27" s="95"/>
       <c r="S27" s="71"/>
@@ -5909,38 +5900,38 @@
     <row r="28" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B28" s="69"/>
       <c r="C28" s="94"/>
-      <c r="D28" s="220"/>
-      <c r="E28" s="220"/>
-      <c r="F28" s="221" t="str">
+      <c r="D28" s="213"/>
+      <c r="E28" s="213"/>
+      <c r="F28" s="289" t="str">
         <f>IF(AND(I19&lt;&gt;"", Q25&lt;&gt;""),(I19*Q25),"")</f>
         <v/>
       </c>
-      <c r="G28" s="221"/>
-      <c r="H28" s="211" t="str">
+      <c r="G28" s="289"/>
+      <c r="H28" s="227" t="str">
         <f>IF(AND(D28&gt;0,F28),(D28-F28)/F28,"")</f>
         <v/>
       </c>
-      <c r="I28" s="211"/>
+      <c r="I28" s="227"/>
       <c r="J28" s="81"/>
       <c r="K28" s="81"/>
-      <c r="L28" s="216" t="s">
+      <c r="L28" s="287" t="s">
         <v>215</v>
       </c>
-      <c r="M28" s="216"/>
-      <c r="N28" s="216"/>
-      <c r="O28" s="216"/>
-      <c r="P28" s="217"/>
+      <c r="M28" s="287"/>
+      <c r="N28" s="287"/>
+      <c r="O28" s="287"/>
+      <c r="P28" s="288"/>
       <c r="Q28" s="108" t="str">
         <f>IF(AND(Q26&lt;&gt;"",Q25&lt;&gt;""),Q25/(Q26/3600),"")</f>
         <v/>
       </c>
       <c r="R28" s="95"/>
       <c r="S28" s="71"/>
-      <c r="U28" s="293" t="str">
+      <c r="U28" s="196" t="str">
         <f>IF(H28&lt;&gt;"",IF(ABS(H28)&lt;0.1,"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="V28" s="293" t="str">
+      <c r="V28" s="196" t="str">
         <f>IF(Q28&lt;&gt;"",IF(Q28&gt;=4,"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -5968,44 +5959,44 @@
     <row r="30" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B30" s="69"/>
       <c r="C30" s="94"/>
-      <c r="D30" s="218" t="s">
+      <c r="D30" s="221" t="s">
         <v>220</v>
       </c>
-      <c r="E30" s="219"/>
-      <c r="F30" s="219"/>
-      <c r="G30" s="219"/>
-      <c r="H30" s="219"/>
-      <c r="I30" s="256"/>
+      <c r="E30" s="222"/>
+      <c r="F30" s="222"/>
+      <c r="G30" s="222"/>
+      <c r="H30" s="222"/>
+      <c r="I30" s="244"/>
       <c r="J30" s="81"/>
-      <c r="K30" s="218" t="s">
+      <c r="K30" s="221" t="s">
         <v>222</v>
       </c>
-      <c r="L30" s="219"/>
-      <c r="M30" s="219"/>
-      <c r="N30" s="219"/>
-      <c r="O30" s="219"/>
-      <c r="P30" s="271" t="s">
+      <c r="L30" s="222"/>
+      <c r="M30" s="222"/>
+      <c r="N30" s="222"/>
+      <c r="O30" s="222"/>
+      <c r="P30" s="223" t="s">
         <v>87</v>
       </c>
-      <c r="Q30" s="272"/>
+      <c r="Q30" s="224"/>
       <c r="R30" s="95"/>
       <c r="S30" s="71"/>
     </row>
     <row r="31" spans="2:22" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B31" s="69"/>
       <c r="C31" s="94"/>
-      <c r="D31" s="212" t="s">
+      <c r="D31" s="219" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="213"/>
-      <c r="F31" s="212" t="s">
+      <c r="E31" s="220"/>
+      <c r="F31" s="219" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="213"/>
-      <c r="H31" s="214" t="s">
+      <c r="G31" s="220"/>
+      <c r="H31" s="225" t="s">
         <v>221</v>
       </c>
-      <c r="I31" s="215"/>
+      <c r="I31" s="226"/>
       <c r="J31" s="81"/>
       <c r="K31" s="109" t="s">
         <v>74</v>
@@ -6013,14 +6004,14 @@
       <c r="L31" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="M31" s="212" t="s">
+      <c r="M31" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="N31" s="273"/>
-      <c r="O31" s="212" t="s">
+      <c r="N31" s="228"/>
+      <c r="O31" s="219" t="s">
         <v>76</v>
       </c>
-      <c r="P31" s="213"/>
+      <c r="P31" s="220"/>
       <c r="Q31" s="85" t="s">
         <v>7</v>
       </c>
@@ -6030,33 +6021,33 @@
     <row r="32" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B32" s="69"/>
       <c r="C32" s="94"/>
-      <c r="D32" s="220"/>
-      <c r="E32" s="220"/>
-      <c r="F32" s="220"/>
-      <c r="G32" s="220"/>
-      <c r="H32" s="211" t="str">
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="227" t="str">
         <f>IF(F32&gt;0,(D32-F32)/F32,"")</f>
         <v/>
       </c>
-      <c r="I32" s="211"/>
+      <c r="I32" s="227"/>
       <c r="J32" s="81"/>
       <c r="K32" s="118"/>
       <c r="L32" s="113"/>
-      <c r="M32" s="220"/>
-      <c r="N32" s="220"/>
-      <c r="O32" s="220"/>
-      <c r="P32" s="220"/>
+      <c r="M32" s="213"/>
+      <c r="N32" s="213"/>
+      <c r="O32" s="213"/>
+      <c r="P32" s="213"/>
       <c r="Q32" s="101" t="str">
         <f>IF(O32&lt;&gt;"",IF(AND(O32&lt;=8,O32&gt;=2),"Oui","Non"),"")</f>
         <v/>
       </c>
       <c r="R32" s="95"/>
       <c r="S32" s="71"/>
-      <c r="U32" s="293" t="str">
+      <c r="U32" s="196" t="str">
         <f>IF(O32&lt;&gt;"",IF(Q32="Oui","Validé","Non validé"), "Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="V32" s="293" t="str">
+      <c r="V32" s="196" t="str">
         <f>IF(H32&lt;&gt;"",IF(ABS(H32)&lt;0.03,"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -6103,24 +6094,24 @@
     </row>
     <row r="35" spans="2:21" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B35" s="69"/>
-      <c r="C35" s="241" t="s">
+      <c r="C35" s="214" t="s">
         <v>261</v>
       </c>
-      <c r="D35" s="242"/>
-      <c r="E35" s="242"/>
-      <c r="F35" s="242"/>
-      <c r="G35" s="242"/>
-      <c r="H35" s="242"/>
-      <c r="I35" s="242"/>
-      <c r="J35" s="242"/>
-      <c r="K35" s="242"/>
-      <c r="L35" s="242"/>
-      <c r="M35" s="242"/>
-      <c r="N35" s="242"/>
-      <c r="O35" s="242"/>
-      <c r="P35" s="242"/>
-      <c r="Q35" s="242"/>
-      <c r="R35" s="243"/>
+      <c r="D35" s="215"/>
+      <c r="E35" s="215"/>
+      <c r="F35" s="215"/>
+      <c r="G35" s="215"/>
+      <c r="H35" s="215"/>
+      <c r="I35" s="215"/>
+      <c r="J35" s="215"/>
+      <c r="K35" s="215"/>
+      <c r="L35" s="215"/>
+      <c r="M35" s="215"/>
+      <c r="N35" s="215"/>
+      <c r="O35" s="215"/>
+      <c r="P35" s="215"/>
+      <c r="Q35" s="215"/>
+      <c r="R35" s="216"/>
       <c r="S35" s="71"/>
     </row>
     <row r="36" spans="2:21" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -6146,44 +6137,46 @@
     <row r="37" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="69"/>
       <c r="C37" s="94"/>
-      <c r="D37" s="269"/>
-      <c r="E37" s="269"/>
-      <c r="F37" s="269"/>
-      <c r="G37" s="269"/>
-      <c r="H37" s="269"/>
-      <c r="I37" s="269"/>
-      <c r="J37" s="269"/>
-      <c r="K37" s="269"/>
-      <c r="L37" s="269"/>
-      <c r="M37" s="269"/>
-      <c r="N37" s="269"/>
-      <c r="O37" s="269"/>
-      <c r="P37" s="269"/>
-      <c r="Q37" s="269"/>
+      <c r="D37" s="217" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="217"/>
+      <c r="F37" s="217"/>
+      <c r="G37" s="217"/>
+      <c r="H37" s="217"/>
+      <c r="I37" s="217"/>
+      <c r="J37" s="217"/>
+      <c r="K37" s="217"/>
+      <c r="L37" s="217"/>
+      <c r="M37" s="217"/>
+      <c r="N37" s="217"/>
+      <c r="O37" s="217"/>
+      <c r="P37" s="217"/>
+      <c r="Q37" s="217"/>
       <c r="R37" s="95"/>
       <c r="S37" s="71"/>
     </row>
     <row r="38" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="69"/>
       <c r="C38" s="94"/>
-      <c r="D38" s="270" t="s">
+      <c r="D38" s="218" t="s">
         <v>224</v>
       </c>
-      <c r="E38" s="270"/>
-      <c r="F38" s="270"/>
-      <c r="G38" s="270"/>
-      <c r="H38" s="270"/>
-      <c r="I38" s="270"/>
-      <c r="J38" s="270" t="s">
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
+      <c r="G38" s="218"/>
+      <c r="H38" s="218"/>
+      <c r="I38" s="218"/>
+      <c r="J38" s="218" t="s">
         <v>184</v>
       </c>
-      <c r="K38" s="270"/>
-      <c r="L38" s="270"/>
-      <c r="M38" s="270"/>
-      <c r="N38" s="270" t="s">
+      <c r="K38" s="218"/>
+      <c r="L38" s="218"/>
+      <c r="M38" s="218"/>
+      <c r="N38" s="218" t="s">
         <v>187</v>
       </c>
-      <c r="O38" s="270"/>
+      <c r="O38" s="218"/>
       <c r="P38" s="92" t="s">
         <v>198</v>
       </c>
@@ -6192,7 +6185,7 @@
       </c>
       <c r="R38" s="95"/>
       <c r="S38" s="71"/>
-      <c r="U38" s="293" t="s">
+      <c r="U38" s="196" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6202,34 +6195,34 @@
       <c r="D39" s="93">
         <v>1</v>
       </c>
-      <c r="E39" s="276" t="str">
+      <c r="E39" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D39+2,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F39" s="277"/>
-      <c r="G39" s="277"/>
-      <c r="H39" s="277"/>
-      <c r="I39" s="278"/>
-      <c r="J39" s="276" t="str">
+        <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
+      </c>
+      <c r="F39" s="209"/>
+      <c r="G39" s="209"/>
+      <c r="H39" s="209"/>
+      <c r="I39" s="210"/>
+      <c r="J39" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D39+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D39+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K39" s="277"/>
-      <c r="L39" s="277"/>
-      <c r="M39" s="278"/>
-      <c r="N39" s="279"/>
-      <c r="O39" s="280"/>
+        <v>En cas d'accès nécessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
+      </c>
+      <c r="K39" s="209"/>
+      <c r="L39" s="209"/>
+      <c r="M39" s="210"/>
+      <c r="N39" s="211"/>
+      <c r="O39" s="212"/>
       <c r="P39" s="83">
         <f>IF(OR(N39 = "Validé",N39="Réserve",N39="Oui"),Q39,0)</f>
         <v>0</v>
       </c>
-      <c r="Q39" s="83" t="str">
+      <c r="Q39" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D39+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="R39" s="95"/>
       <c r="S39" s="71"/>
-      <c r="U39" s="293" t="s">
+      <c r="U39" s="196" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6239,34 +6232,34 @@
       <c r="D40" s="93">
         <v>2</v>
       </c>
-      <c r="E40" s="276" t="str">
+      <c r="E40" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D40+2,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F40" s="277"/>
-      <c r="G40" s="277"/>
-      <c r="H40" s="277"/>
-      <c r="I40" s="278"/>
-      <c r="J40" s="276" t="str">
+        <v>Le point de prélèvement est-il correctement implanté ?</v>
+      </c>
+      <c r="F40" s="209"/>
+      <c r="G40" s="209"/>
+      <c r="H40" s="209"/>
+      <c r="I40" s="210"/>
+      <c r="J40" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D40+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D40+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="K40" s="277"/>
-      <c r="L40" s="277"/>
-      <c r="M40" s="278"/>
-      <c r="N40" s="279"/>
-      <c r="O40" s="280"/>
+      <c r="K40" s="209"/>
+      <c r="L40" s="209"/>
+      <c r="M40" s="210"/>
+      <c r="N40" s="211"/>
+      <c r="O40" s="212"/>
       <c r="P40" s="83">
         <f t="shared" ref="P40:P48" si="0">IF(OR(N40 = "Validé",N40="Réserve",N40="Oui"),Q40,0)</f>
         <v>0</v>
       </c>
-      <c r="Q40" s="83" t="str">
+      <c r="Q40" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D40+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="R40" s="95"/>
       <c r="S40" s="71"/>
-      <c r="U40" s="293" t="s">
+      <c r="U40" s="196" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6276,34 +6269,35 @@
       <c r="D41" s="93">
         <v>3</v>
       </c>
-      <c r="E41" s="276" t="str">
+      <c r="E41" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D41+2,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F41" s="277"/>
-      <c r="G41" s="277"/>
-      <c r="H41" s="277"/>
-      <c r="I41" s="278"/>
-      <c r="J41" s="276" t="str">
+        <v>La propreté et l'état d'entretien du dispositif de prélèvement sont-ils satisfaisants ?</v>
+      </c>
+      <c r="F41" s="209"/>
+      <c r="G41" s="209"/>
+      <c r="H41" s="209"/>
+      <c r="I41" s="210"/>
+      <c r="J41" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D41+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D41+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K41" s="277"/>
-      <c r="L41" s="277"/>
-      <c r="M41" s="278"/>
-      <c r="N41" s="279"/>
-      <c r="O41" s="280"/>
+        <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité du prélèvement doit entrainer un jugement à "Non Validé".
+Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité du prélèvement doit avoir un jugement "Validé avec réserve".</v>
+      </c>
+      <c r="K41" s="209"/>
+      <c r="L41" s="209"/>
+      <c r="M41" s="210"/>
+      <c r="N41" s="211"/>
+      <c r="O41" s="212"/>
       <c r="P41" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="83" t="str">
+      <c r="Q41" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D41+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R41" s="95"/>
       <c r="S41" s="71"/>
-      <c r="U41" s="293" t="s">
+      <c r="U41" s="196" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6313,37 +6307,37 @@
       <c r="D42" s="93">
         <v>4</v>
       </c>
-      <c r="E42" s="276" t="str">
+      <c r="E42" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D42+2,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F42" s="277"/>
-      <c r="G42" s="277"/>
-      <c r="H42" s="277"/>
-      <c r="I42" s="278"/>
-      <c r="J42" s="276" t="str">
+        <v>Le dispositif de prélèvement présente t-il un état de fonctionnement satisfaisant, son diamètre est-il ≥ à 9 mm ?</v>
+      </c>
+      <c r="F42" s="209"/>
+      <c r="G42" s="209"/>
+      <c r="H42" s="209"/>
+      <c r="I42" s="210"/>
+      <c r="J42" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="K42" s="277"/>
-      <c r="L42" s="277"/>
-      <c r="M42" s="278"/>
-      <c r="N42" s="279" t="str">
+      <c r="K42" s="209"/>
+      <c r="L42" s="209"/>
+      <c r="M42" s="210"/>
+      <c r="N42" s="211" t="str">
         <f>IF(E42="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U14,"Non contrôlé"))</f>
-        <v>Non applicable</v>
-      </c>
-      <c r="O42" s="280"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="O42" s="212"/>
       <c r="P42" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q42" s="83" t="str">
+      <c r="Q42" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R42" s="95"/>
       <c r="S42" s="71"/>
-      <c r="U42" s="293" t="s">
+      <c r="U42" s="196" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6353,37 +6347,37 @@
       <c r="D43" s="93">
         <v>5</v>
       </c>
-      <c r="E43" s="276" t="str">
+      <c r="E43" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D43+2,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F43" s="277"/>
-      <c r="G43" s="277"/>
-      <c r="H43" s="277"/>
-      <c r="I43" s="278"/>
-      <c r="J43" s="276" t="str">
+        <v>Le volume de prélèvement par cycle est-il ≥ à 50 ml et est-il répétable à ± 5 % ?</v>
+      </c>
+      <c r="F43" s="209"/>
+      <c r="G43" s="209"/>
+      <c r="H43" s="209"/>
+      <c r="I43" s="210"/>
+      <c r="J43" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K43" s="277"/>
-      <c r="L43" s="277"/>
-      <c r="M43" s="278"/>
-      <c r="N43" s="279" t="str">
+        <v>Contrôle à réaliser sur 3 prélèvements</v>
+      </c>
+      <c r="K43" s="209"/>
+      <c r="L43" s="209"/>
+      <c r="M43" s="210"/>
+      <c r="N43" s="211" t="str">
         <f>IF(E43="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U19,"Non contrôlé"))</f>
-        <v>Non applicable</v>
-      </c>
-      <c r="O43" s="280"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="O43" s="212"/>
       <c r="P43" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="83" t="str">
+      <c r="Q43" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R43" s="95"/>
       <c r="S43" s="71"/>
-      <c r="U43" s="293" t="s">
+      <c r="U43" s="196" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6393,37 +6387,37 @@
       <c r="D44" s="93">
         <v>6</v>
       </c>
-      <c r="E44" s="276" t="str">
+      <c r="E44" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D44+2,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="F44" s="277"/>
-      <c r="G44" s="277"/>
-      <c r="H44" s="277"/>
-      <c r="I44" s="278"/>
-      <c r="J44" s="276" t="str">
+      <c r="F44" s="209"/>
+      <c r="G44" s="209"/>
+      <c r="H44" s="209"/>
+      <c r="I44" s="210"/>
+      <c r="J44" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K44" s="277"/>
-      <c r="L44" s="277"/>
-      <c r="M44" s="278"/>
-      <c r="N44" s="279" t="str">
+        <v>question non applicable</v>
+      </c>
+      <c r="K44" s="209"/>
+      <c r="L44" s="209"/>
+      <c r="M44" s="210"/>
+      <c r="N44" s="211" t="str">
         <f>IF(E44="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U24,"Non contrôlé"))</f>
         <v>Non applicable</v>
       </c>
-      <c r="O44" s="280"/>
+      <c r="O44" s="212"/>
       <c r="P44" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="83" t="str">
+      <c r="Q44" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R44" s="95"/>
       <c r="S44" s="71"/>
-      <c r="U44" s="293" t="s">
+      <c r="U44" s="196" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6433,37 +6427,37 @@
       <c r="D45" s="93">
         <v>7</v>
       </c>
-      <c r="E45" s="276" t="str">
+      <c r="E45" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D45+2,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F45" s="277"/>
-      <c r="G45" s="277"/>
-      <c r="H45" s="277"/>
-      <c r="I45" s="278"/>
-      <c r="J45" s="276" t="str">
+        <v>La vanne de prélèvement est-elle asservie au débit, ou au volume écoulé, et assure-t-elle un nombre de prélèvements égal, en moyenne, à au moins à 6 par heure de rejet effectif ? soit 144 prélèvements unitaires par 24h de rejet.</v>
+      </c>
+      <c r="F45" s="209"/>
+      <c r="G45" s="209"/>
+      <c r="H45" s="209"/>
+      <c r="I45" s="210"/>
+      <c r="J45" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K45" s="277"/>
-      <c r="L45" s="277"/>
-      <c r="M45" s="278"/>
-      <c r="N45" s="279" t="str">
+        <v>Tolérance de validation à 4 prélèvements par heure de rejet (soit 96 prélèvements/jour), sur justification d'un évènement exceptionnel.</v>
+      </c>
+      <c r="K45" s="209"/>
+      <c r="L45" s="209"/>
+      <c r="M45" s="210"/>
+      <c r="N45" s="211" t="str">
         <f>IF(E45="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),V28,"Non contrôlé"))</f>
-        <v>Non applicable</v>
-      </c>
-      <c r="O45" s="280"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="O45" s="212"/>
       <c r="P45" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q45" s="83" t="str">
+      <c r="Q45" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="R45" s="95"/>
       <c r="S45" s="71"/>
-      <c r="U45" s="293" t="s">
+      <c r="U45" s="196" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6473,37 +6467,37 @@
       <c r="D46" s="93">
         <v>8</v>
       </c>
-      <c r="E46" s="276" t="str">
+      <c r="E46" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D46+2,FALSE),"-")</f>
+        <v xml:space="preserve"> Les horaires de prélèvement et de totalisation des débits sont-ils synchronisés ?</v>
+      </c>
+      <c r="F46" s="209"/>
+      <c r="G46" s="209"/>
+      <c r="H46" s="209"/>
+      <c r="I46" s="210"/>
+      <c r="J46" s="208" t="str">
+        <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v>-</v>
       </c>
-      <c r="F46" s="277"/>
-      <c r="G46" s="277"/>
-      <c r="H46" s="277"/>
-      <c r="I46" s="278"/>
-      <c r="J46" s="276" t="str">
-        <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K46" s="277"/>
-      <c r="L46" s="277"/>
-      <c r="M46" s="278"/>
-      <c r="N46" s="279" t="str">
+      <c r="K46" s="209"/>
+      <c r="L46" s="209"/>
+      <c r="M46" s="210"/>
+      <c r="N46" s="211" t="str">
         <f>IF(E46="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),V28,"Non contrôlé"))</f>
-        <v>Non applicable</v>
-      </c>
-      <c r="O46" s="280"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="O46" s="212"/>
       <c r="P46" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q46" s="83" t="str">
+      <c r="Q46" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R46" s="95"/>
       <c r="S46" s="71"/>
-      <c r="U46" s="293" t="s">
+      <c r="U46" s="196" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6513,37 +6507,37 @@
       <c r="D47" s="93">
         <v>9</v>
       </c>
-      <c r="E47" s="276" t="str">
+      <c r="E47" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D47+2,FALSE),"-")</f>
+        <v>La température de l'enceinte de prélèvement est-elle adaptée? Si elle est réfrigérée, sa température est-elle maîtrisée à 5°C ± 3°C ?</v>
+      </c>
+      <c r="F47" s="209"/>
+      <c r="G47" s="209"/>
+      <c r="H47" s="209"/>
+      <c r="I47" s="210"/>
+      <c r="J47" s="208" t="str">
+        <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v>-</v>
       </c>
-      <c r="F47" s="277"/>
-      <c r="G47" s="277"/>
-      <c r="H47" s="277"/>
-      <c r="I47" s="278"/>
-      <c r="J47" s="276" t="str">
-        <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K47" s="277"/>
-      <c r="L47" s="277"/>
-      <c r="M47" s="278"/>
-      <c r="N47" s="279" t="str">
+      <c r="K47" s="209"/>
+      <c r="L47" s="209"/>
+      <c r="M47" s="210"/>
+      <c r="N47" s="211" t="str">
         <f>IF(E47="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U32,"Non contrôlé"))</f>
-        <v>Non applicable</v>
-      </c>
-      <c r="O47" s="280"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="O47" s="212"/>
       <c r="P47" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="83" t="str">
+      <c r="Q47" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="R47" s="95"/>
       <c r="S47" s="71"/>
-      <c r="U47" s="293" t="s">
+      <c r="U47" s="196" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6553,87 +6547,87 @@
       <c r="D48" s="93">
         <v>10</v>
       </c>
-      <c r="E48" s="276" t="str">
+      <c r="E48" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D48+2,FALSE),"-")</f>
+        <v>L'écart entre le volume théorique et le volume prélevé est-il ≤ à 10% ?</v>
+      </c>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="210"/>
+      <c r="J48" s="208" t="str">
+        <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v>-</v>
       </c>
-      <c r="F48" s="277"/>
-      <c r="G48" s="277"/>
-      <c r="H48" s="277"/>
-      <c r="I48" s="278"/>
-      <c r="J48" s="276" t="str">
-        <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="K48" s="277"/>
-      <c r="L48" s="277"/>
-      <c r="M48" s="278"/>
-      <c r="N48" s="279" t="str">
+      <c r="K48" s="209"/>
+      <c r="L48" s="209"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="211" t="str">
         <f>IF(E48="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U28,"Non contrôlé"))</f>
-        <v>Non applicable</v>
-      </c>
-      <c r="O48" s="280"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="O48" s="212"/>
       <c r="P48" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="83" t="str">
+      <c r="Q48" s="83">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="R48" s="95"/>
       <c r="S48" s="71"/>
-      <c r="U48" s="293" t="s">
+      <c r="U48" s="196" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="49" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="69"/>
       <c r="C49" s="94"/>
-      <c r="D49" s="281" t="s">
+      <c r="D49" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="E49" s="282"/>
-      <c r="F49" s="282"/>
-      <c r="G49" s="282"/>
-      <c r="H49" s="282"/>
-      <c r="I49" s="282"/>
-      <c r="J49" s="282"/>
-      <c r="K49" s="282"/>
-      <c r="L49" s="282"/>
-      <c r="M49" s="283"/>
-      <c r="N49" s="284"/>
-      <c r="O49" s="284"/>
-      <c r="P49" s="284" t="s">
+      <c r="E49" s="199"/>
+      <c r="F49" s="199"/>
+      <c r="G49" s="199"/>
+      <c r="H49" s="199"/>
+      <c r="I49" s="199"/>
+      <c r="J49" s="199"/>
+      <c r="K49" s="199"/>
+      <c r="L49" s="199"/>
+      <c r="M49" s="200"/>
+      <c r="N49" s="201"/>
+      <c r="O49" s="201"/>
+      <c r="P49" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="284"/>
+      <c r="Q49" s="201"/>
       <c r="R49" s="95"/>
       <c r="S49" s="71"/>
     </row>
     <row r="50" spans="2:19" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="69"/>
       <c r="C50" s="94"/>
-      <c r="D50" s="285"/>
-      <c r="E50" s="286"/>
-      <c r="F50" s="286"/>
-      <c r="G50" s="286"/>
-      <c r="H50" s="286"/>
-      <c r="I50" s="286"/>
-      <c r="J50" s="286"/>
-      <c r="K50" s="286"/>
-      <c r="L50" s="286"/>
-      <c r="M50" s="287"/>
-      <c r="N50" s="288" t="str">
+      <c r="D50" s="202"/>
+      <c r="E50" s="203"/>
+      <c r="F50" s="203"/>
+      <c r="G50" s="203"/>
+      <c r="H50" s="203"/>
+      <c r="I50" s="203"/>
+      <c r="J50" s="203"/>
+      <c r="K50" s="203"/>
+      <c r="L50" s="203"/>
+      <c r="M50" s="204"/>
+      <c r="N50" s="205" t="str">
         <f>IF(P50&gt;80,"Validé",IF(P50&lt;70,"Non Validé", "Réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="O50" s="288"/>
-      <c r="P50" s="289">
+      <c r="O50" s="205"/>
+      <c r="P50" s="206">
         <f>IF(SUM(P39:P48)&gt;100,100,SUM(P39:P48))</f>
         <v>0</v>
       </c>
-      <c r="Q50" s="290"/>
+      <c r="Q50" s="207"/>
       <c r="R50" s="95"/>
       <c r="S50" s="71"/>
     </row>
@@ -6679,126 +6673,126 @@
     </row>
     <row r="53" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B53" s="69"/>
-      <c r="C53" s="241" t="s">
+      <c r="C53" s="214" t="s">
         <v>262</v>
       </c>
-      <c r="D53" s="242"/>
-      <c r="E53" s="242"/>
-      <c r="F53" s="242"/>
-      <c r="G53" s="242"/>
-      <c r="H53" s="242"/>
-      <c r="I53" s="242"/>
-      <c r="J53" s="242"/>
-      <c r="K53" s="242"/>
-      <c r="L53" s="242"/>
-      <c r="M53" s="242"/>
-      <c r="N53" s="242"/>
-      <c r="O53" s="242"/>
-      <c r="P53" s="242"/>
-      <c r="Q53" s="242"/>
-      <c r="R53" s="243"/>
+      <c r="D53" s="215"/>
+      <c r="E53" s="215"/>
+      <c r="F53" s="215"/>
+      <c r="G53" s="215"/>
+      <c r="H53" s="215"/>
+      <c r="I53" s="215"/>
+      <c r="J53" s="215"/>
+      <c r="K53" s="215"/>
+      <c r="L53" s="215"/>
+      <c r="M53" s="215"/>
+      <c r="N53" s="215"/>
+      <c r="O53" s="215"/>
+      <c r="P53" s="215"/>
+      <c r="Q53" s="215"/>
+      <c r="R53" s="216"/>
       <c r="S53" s="71"/>
     </row>
     <row r="54" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B54" s="69"/>
-      <c r="C54" s="244" t="s">
+      <c r="C54" s="232" t="s">
         <v>199</v>
       </c>
-      <c r="D54" s="245"/>
-      <c r="E54" s="245"/>
-      <c r="F54" s="245"/>
-      <c r="G54" s="245"/>
-      <c r="H54" s="245"/>
-      <c r="I54" s="245"/>
-      <c r="J54" s="245"/>
-      <c r="K54" s="245"/>
-      <c r="L54" s="245"/>
-      <c r="M54" s="245"/>
-      <c r="N54" s="245"/>
-      <c r="O54" s="245"/>
-      <c r="P54" s="245"/>
-      <c r="Q54" s="245"/>
-      <c r="R54" s="246"/>
+      <c r="D54" s="233"/>
+      <c r="E54" s="233"/>
+      <c r="F54" s="233"/>
+      <c r="G54" s="233"/>
+      <c r="H54" s="233"/>
+      <c r="I54" s="233"/>
+      <c r="J54" s="233"/>
+      <c r="K54" s="233"/>
+      <c r="L54" s="233"/>
+      <c r="M54" s="233"/>
+      <c r="N54" s="233"/>
+      <c r="O54" s="233"/>
+      <c r="P54" s="233"/>
+      <c r="Q54" s="233"/>
+      <c r="R54" s="234"/>
       <c r="S54" s="71"/>
     </row>
     <row r="55" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="69"/>
-      <c r="C55" s="247"/>
-      <c r="D55" s="245"/>
-      <c r="E55" s="245"/>
-      <c r="F55" s="245"/>
-      <c r="G55" s="245"/>
-      <c r="H55" s="245"/>
-      <c r="I55" s="245"/>
-      <c r="J55" s="245"/>
-      <c r="K55" s="245"/>
-      <c r="L55" s="245"/>
-      <c r="M55" s="245"/>
-      <c r="N55" s="245"/>
-      <c r="O55" s="245"/>
-      <c r="P55" s="245"/>
-      <c r="Q55" s="245"/>
-      <c r="R55" s="246"/>
+      <c r="C55" s="235"/>
+      <c r="D55" s="233"/>
+      <c r="E55" s="233"/>
+      <c r="F55" s="233"/>
+      <c r="G55" s="233"/>
+      <c r="H55" s="233"/>
+      <c r="I55" s="233"/>
+      <c r="J55" s="233"/>
+      <c r="K55" s="233"/>
+      <c r="L55" s="233"/>
+      <c r="M55" s="233"/>
+      <c r="N55" s="233"/>
+      <c r="O55" s="233"/>
+      <c r="P55" s="233"/>
+      <c r="Q55" s="233"/>
+      <c r="R55" s="234"/>
       <c r="S55" s="71"/>
     </row>
     <row r="56" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="69"/>
-      <c r="C56" s="247"/>
-      <c r="D56" s="245"/>
-      <c r="E56" s="245"/>
-      <c r="F56" s="245"/>
-      <c r="G56" s="245"/>
-      <c r="H56" s="245"/>
-      <c r="I56" s="245"/>
-      <c r="J56" s="245"/>
-      <c r="K56" s="245"/>
-      <c r="L56" s="245"/>
-      <c r="M56" s="245"/>
-      <c r="N56" s="245"/>
-      <c r="O56" s="245"/>
-      <c r="P56" s="245"/>
-      <c r="Q56" s="245"/>
-      <c r="R56" s="246"/>
+      <c r="C56" s="235"/>
+      <c r="D56" s="233"/>
+      <c r="E56" s="233"/>
+      <c r="F56" s="233"/>
+      <c r="G56" s="233"/>
+      <c r="H56" s="233"/>
+      <c r="I56" s="233"/>
+      <c r="J56" s="233"/>
+      <c r="K56" s="233"/>
+      <c r="L56" s="233"/>
+      <c r="M56" s="233"/>
+      <c r="N56" s="233"/>
+      <c r="O56" s="233"/>
+      <c r="P56" s="233"/>
+      <c r="Q56" s="233"/>
+      <c r="R56" s="234"/>
       <c r="S56" s="71"/>
     </row>
     <row r="57" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="69"/>
-      <c r="C57" s="247"/>
-      <c r="D57" s="245"/>
-      <c r="E57" s="245"/>
-      <c r="F57" s="245"/>
-      <c r="G57" s="245"/>
-      <c r="H57" s="245"/>
-      <c r="I57" s="245"/>
-      <c r="J57" s="245"/>
-      <c r="K57" s="245"/>
-      <c r="L57" s="245"/>
-      <c r="M57" s="245"/>
-      <c r="N57" s="245"/>
-      <c r="O57" s="245"/>
-      <c r="P57" s="245"/>
-      <c r="Q57" s="245"/>
-      <c r="R57" s="246"/>
+      <c r="C57" s="235"/>
+      <c r="D57" s="233"/>
+      <c r="E57" s="233"/>
+      <c r="F57" s="233"/>
+      <c r="G57" s="233"/>
+      <c r="H57" s="233"/>
+      <c r="I57" s="233"/>
+      <c r="J57" s="233"/>
+      <c r="K57" s="233"/>
+      <c r="L57" s="233"/>
+      <c r="M57" s="233"/>
+      <c r="N57" s="233"/>
+      <c r="O57" s="233"/>
+      <c r="P57" s="233"/>
+      <c r="Q57" s="233"/>
+      <c r="R57" s="234"/>
       <c r="S57" s="71"/>
     </row>
     <row r="58" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B58" s="69"/>
-      <c r="C58" s="248"/>
-      <c r="D58" s="249"/>
-      <c r="E58" s="249"/>
-      <c r="F58" s="249"/>
-      <c r="G58" s="249"/>
-      <c r="H58" s="249"/>
-      <c r="I58" s="249"/>
-      <c r="J58" s="249"/>
-      <c r="K58" s="249"/>
-      <c r="L58" s="249"/>
-      <c r="M58" s="249"/>
-      <c r="N58" s="249"/>
-      <c r="O58" s="249"/>
-      <c r="P58" s="249"/>
-      <c r="Q58" s="249"/>
-      <c r="R58" s="250"/>
+      <c r="C58" s="236"/>
+      <c r="D58" s="237"/>
+      <c r="E58" s="237"/>
+      <c r="F58" s="237"/>
+      <c r="G58" s="237"/>
+      <c r="H58" s="237"/>
+      <c r="I58" s="237"/>
+      <c r="J58" s="237"/>
+      <c r="K58" s="237"/>
+      <c r="L58" s="237"/>
+      <c r="M58" s="237"/>
+      <c r="N58" s="237"/>
+      <c r="O58" s="237"/>
+      <c r="P58" s="237"/>
+      <c r="Q58" s="237"/>
+      <c r="R58" s="238"/>
       <c r="S58" s="71"/>
     </row>
     <row r="59" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -6822,63 +6816,60 @@
       <c r="S59" s="75"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NYmTS4XfM8RLBQYNDVexmQoNyuhhuA6XqsCXJuMD7s2zRTZJqlADGesqRVjZIACa8Utm1KkNPNuFPnBmpILIYg==" saltValue="M+1cXOxQEKV8DyZc0311bQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="miuWYHEJEH83k18AURW2vDLzCwXzZQS+VdMHxK9uE+HO7zVGxUCBxB/+ZU8sbtGikoWJD87bW71RvYTRjGYghw==" saltValue="W41jshMzvoeNNF5b4T1QlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="131">
-    <mergeCell ref="D49:M49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="D50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="E47:I47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="E48:I48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="C35:R35"/>
-    <mergeCell ref="D37:Q37"/>
-    <mergeCell ref="D38:I38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="K30:O30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="L25:P25"/>
+    <mergeCell ref="L21:Q21"/>
+    <mergeCell ref="L22:Q22"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="L26:P26"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="L28:P28"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="C2:R2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="D17:M17"/>
+    <mergeCell ref="G11:Q11"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:O5"/>
     <mergeCell ref="C53:R53"/>
     <mergeCell ref="C54:R58"/>
     <mergeCell ref="C6:D6"/>
@@ -6903,58 +6894,61 @@
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="C2:R2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="D17:M17"/>
-    <mergeCell ref="G11:Q11"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="L25:P25"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="L22:Q22"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="L26:P26"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="L28:P28"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="C35:R35"/>
+    <mergeCell ref="D37:Q37"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="K30:O30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="D49:M49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="D50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="E48:I48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="N48:O48"/>
   </mergeCells>
   <conditionalFormatting sqref="H28:I28">
     <cfRule type="expression" dxfId="22" priority="14">
@@ -7647,91 +7641,91 @@
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:603" ht="37.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="179"/>
-      <c r="B2" s="180" t="s">
+      <c r="A2" s="178"/>
+      <c r="B2" s="179" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="182"/>
-      <c r="L2" s="183"/>
-      <c r="M2" s="183"/>
-      <c r="N2" s="182"/>
-      <c r="O2" s="182"/>
-      <c r="P2" s="183"/>
-      <c r="Q2" s="183"/>
-      <c r="R2" s="182"/>
-      <c r="S2" s="182"/>
-      <c r="T2" s="183"/>
-      <c r="U2" s="183"/>
-      <c r="V2" s="184" t="s">
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="181"/>
+      <c r="K2" s="181"/>
+      <c r="L2" s="182"/>
+      <c r="M2" s="182"/>
+      <c r="N2" s="181"/>
+      <c r="O2" s="181"/>
+      <c r="P2" s="182"/>
+      <c r="Q2" s="182"/>
+      <c r="R2" s="181"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="W2" s="185"/>
-      <c r="X2" s="186"/>
-      <c r="Y2" s="186"/>
-      <c r="Z2" s="185"/>
-      <c r="AA2" s="185"/>
-      <c r="AB2" s="186"/>
-      <c r="AC2" s="186"/>
-      <c r="AD2" s="185"/>
-      <c r="AE2" s="185"/>
-      <c r="AF2" s="186"/>
-      <c r="AG2" s="186"/>
-      <c r="AH2" s="185"/>
-      <c r="AI2" s="185"/>
-      <c r="AJ2" s="186"/>
-      <c r="AK2" s="186"/>
-      <c r="AL2" s="185"/>
-      <c r="AM2" s="185"/>
-      <c r="AN2" s="186"/>
-      <c r="AO2" s="186"/>
-      <c r="AP2" s="185"/>
-      <c r="AQ2" s="185"/>
-      <c r="AR2" s="186"/>
-      <c r="AS2" s="186"/>
-      <c r="AT2" s="185"/>
-      <c r="AU2" s="185"/>
-      <c r="AV2" s="186"/>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="185"/>
-      <c r="AY2" s="185"/>
-      <c r="AZ2" s="186"/>
-      <c r="BA2" s="186"/>
-      <c r="BB2" s="185"/>
-      <c r="BC2" s="185"/>
-      <c r="BD2" s="186"/>
-      <c r="BE2" s="186"/>
-      <c r="BF2" s="187" t="s">
+      <c r="W2" s="184"/>
+      <c r="X2" s="185"/>
+      <c r="Y2" s="185"/>
+      <c r="Z2" s="184"/>
+      <c r="AA2" s="184"/>
+      <c r="AB2" s="185"/>
+      <c r="AC2" s="185"/>
+      <c r="AD2" s="184"/>
+      <c r="AE2" s="184"/>
+      <c r="AF2" s="185"/>
+      <c r="AG2" s="185"/>
+      <c r="AH2" s="184"/>
+      <c r="AI2" s="184"/>
+      <c r="AJ2" s="185"/>
+      <c r="AK2" s="185"/>
+      <c r="AL2" s="184"/>
+      <c r="AM2" s="184"/>
+      <c r="AN2" s="185"/>
+      <c r="AO2" s="185"/>
+      <c r="AP2" s="184"/>
+      <c r="AQ2" s="184"/>
+      <c r="AR2" s="185"/>
+      <c r="AS2" s="185"/>
+      <c r="AT2" s="184"/>
+      <c r="AU2" s="184"/>
+      <c r="AV2" s="185"/>
+      <c r="AW2" s="185"/>
+      <c r="AX2" s="184"/>
+      <c r="AY2" s="184"/>
+      <c r="AZ2" s="185"/>
+      <c r="BA2" s="185"/>
+      <c r="BB2" s="184"/>
+      <c r="BC2" s="184"/>
+      <c r="BD2" s="185"/>
+      <c r="BE2" s="185"/>
+      <c r="BF2" s="186" t="s">
         <v>344</v>
       </c>
-      <c r="BG2" s="188"/>
-      <c r="BH2" s="188"/>
-      <c r="BI2" s="188"/>
-      <c r="BJ2" s="188"/>
-      <c r="BK2" s="188"/>
-      <c r="BL2" s="188"/>
-      <c r="BM2" s="188"/>
-      <c r="BN2" s="188"/>
-      <c r="BO2" s="188"/>
-      <c r="BP2" s="188"/>
-      <c r="BQ2" s="188"/>
-      <c r="BR2" s="189" t="s">
+      <c r="BG2" s="187"/>
+      <c r="BH2" s="187"/>
+      <c r="BI2" s="187"/>
+      <c r="BJ2" s="187"/>
+      <c r="BK2" s="187"/>
+      <c r="BL2" s="187"/>
+      <c r="BM2" s="187"/>
+      <c r="BN2" s="187"/>
+      <c r="BO2" s="187"/>
+      <c r="BP2" s="187"/>
+      <c r="BQ2" s="187"/>
+      <c r="BR2" s="188" t="s">
         <v>345</v>
       </c>
-      <c r="BS2" s="190"/>
-      <c r="BT2" s="190"/>
-      <c r="BU2" s="190"/>
-      <c r="BV2" s="190"/>
-      <c r="BW2" s="190"/>
-      <c r="BX2" s="190"/>
-      <c r="BY2" s="190"/>
+      <c r="BS2" s="189"/>
+      <c r="BT2" s="189"/>
+      <c r="BU2" s="189"/>
+      <c r="BV2" s="189"/>
+      <c r="BW2" s="189"/>
+      <c r="BX2" s="189"/>
+      <c r="BY2" s="189"/>
       <c r="LK2" s="19"/>
       <c r="MD2" s="19"/>
       <c r="MT2" s="19"/>
@@ -8682,7 +8676,7 @@
         <v>10</v>
       </c>
       <c r="AK7" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL7" s="24" t="s">
         <v>134</v>
@@ -8692,7 +8686,7 @@
         <v>10</v>
       </c>
       <c r="AO7" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP7" s="24" t="s">
         <v>135</v>
@@ -8728,7 +8722,7 @@
         <v>10</v>
       </c>
       <c r="BA7" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB7" s="24" t="s">
         <v>138</v>
@@ -8740,7 +8734,7 @@
         <v>20</v>
       </c>
       <c r="BE7" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BF7" s="24" t="s">
         <v>139</v>
@@ -8829,7 +8823,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J8" s="40" t="s">
         <v>142</v>
@@ -8961,7 +8955,7 @@
         <v>10</v>
       </c>
       <c r="BA8" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB8" s="40" t="s">
         <v>147</v>
@@ -9048,7 +9042,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="156" t="s">
         <v>151</v>
@@ -9060,7 +9054,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9" s="156" t="s">
         <v>149</v>
@@ -9072,7 +9066,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N9" s="156" t="s">
         <v>149</v>
@@ -9084,7 +9078,7 @@
         <v>20</v>
       </c>
       <c r="Q9" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R9" s="156" t="s">
         <v>149</v>
@@ -9096,7 +9090,7 @@
         <v>20</v>
       </c>
       <c r="U9" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V9" s="10" t="s">
         <v>33</v>
@@ -9216,7 +9210,7 @@
         <v>5</v>
       </c>
       <c r="BI9" s="153" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BJ9" s="154" t="s">
         <v>158</v>
@@ -9228,7 +9222,7 @@
         <v>5</v>
       </c>
       <c r="BM9" s="155" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BN9" s="156" t="s">
         <v>160</v>
@@ -9249,7 +9243,7 @@
         <v>279</v>
       </c>
       <c r="BT9" s="158"/>
-      <c r="BU9" s="171" t="s">
+      <c r="BU9" s="170" t="s">
         <v>281</v>
       </c>
       <c r="BV9" s="10" t="s">
@@ -9279,7 +9273,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="47" t="s">
         <v>335</v>
@@ -9291,7 +9285,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J10" s="47" t="s">
         <v>273</v>
@@ -9303,7 +9297,7 @@
         <v>20</v>
       </c>
       <c r="M10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N10" s="47" t="s">
         <v>273</v>
@@ -9315,7 +9309,7 @@
         <v>20</v>
       </c>
       <c r="Q10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R10" s="47" t="s">
         <v>273</v>
@@ -9327,7 +9321,7 @@
         <v>20</v>
       </c>
       <c r="U10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V10" s="44" t="s">
         <v>161</v>
@@ -9419,7 +9413,7 @@
         <v>20</v>
       </c>
       <c r="BA10" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB10" s="40" t="s">
         <v>164</v>
@@ -9431,7 +9425,7 @@
         <v>5</v>
       </c>
       <c r="BE10" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BF10" s="40" t="s">
         <v>34</v>
@@ -9443,7 +9437,7 @@
         <v>5</v>
       </c>
       <c r="BI10" s="122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BJ10" s="130" t="s">
         <v>279</v>
@@ -9464,7 +9458,7 @@
         <v>279</v>
       </c>
       <c r="BP10" s="42"/>
-      <c r="BQ10" s="172" t="s">
+      <c r="BQ10" s="171" t="s">
         <v>281</v>
       </c>
       <c r="BR10" s="44" t="s">
@@ -9484,7 +9478,7 @@
         <v>279</v>
       </c>
       <c r="BX10" s="42"/>
-      <c r="BY10" s="172" t="s">
+      <c r="BY10" s="171" t="s">
         <v>281</v>
       </c>
     </row>
@@ -9502,7 +9496,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="156" t="s">
         <v>336</v>
@@ -9514,7 +9508,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" s="156" t="s">
         <v>277</v>
@@ -9526,7 +9520,7 @@
         <v>20</v>
       </c>
       <c r="M11" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N11" s="156" t="s">
         <v>277</v>
@@ -9538,7 +9532,7 @@
         <v>20</v>
       </c>
       <c r="Q11" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R11" s="156" t="s">
         <v>277</v>
@@ -9550,7 +9544,7 @@
         <v>20</v>
       </c>
       <c r="U11" s="159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V11" s="10" t="s">
         <v>166</v>
@@ -9562,7 +9556,7 @@
         <v>10</v>
       </c>
       <c r="Y11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z11" s="10" t="s">
         <v>166</v>
@@ -9574,7 +9568,7 @@
         <v>10</v>
       </c>
       <c r="AC11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD11" s="10" t="s">
         <v>166</v>
@@ -9586,7 +9580,7 @@
         <v>10</v>
       </c>
       <c r="AG11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AH11" s="10" t="s">
         <v>166</v>
@@ -9598,7 +9592,7 @@
         <v>10</v>
       </c>
       <c r="AK11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL11" s="10" t="s">
         <v>166</v>
@@ -9610,7 +9604,7 @@
         <v>10</v>
       </c>
       <c r="AO11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP11" s="10" t="s">
         <v>166</v>
@@ -9622,7 +9616,7 @@
         <v>10</v>
       </c>
       <c r="AS11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AT11" s="24" t="s">
         <v>337</v>
@@ -9634,7 +9628,7 @@
         <v>15</v>
       </c>
       <c r="AW11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>167</v>
@@ -9646,7 +9640,7 @@
         <v>20</v>
       </c>
       <c r="BA11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB11" s="24" t="s">
         <v>168</v>
@@ -9658,7 +9652,7 @@
         <v>5</v>
       </c>
       <c r="BE11" s="151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BF11" s="24" t="s">
         <v>165</v>
@@ -9672,17 +9666,17 @@
       <c r="BI11" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="BJ11" s="191" t="s">
+      <c r="BJ11" s="190" t="s">
         <v>342</v>
       </c>
-      <c r="BK11" s="192" t="s">
+      <c r="BK11" s="191" t="s">
         <v>276</v>
       </c>
-      <c r="BL11" s="193">
+      <c r="BL11" s="192">
         <v>10</v>
       </c>
-      <c r="BM11" s="194" t="s">
-        <v>40</v>
+      <c r="BM11" s="155" t="s">
+        <v>39</v>
       </c>
       <c r="BN11" s="24" t="s">
         <v>279</v>
@@ -9701,7 +9695,7 @@
         <v>279</v>
       </c>
       <c r="BT11" s="150"/>
-      <c r="BU11" s="173" t="s">
+      <c r="BU11" s="172" t="s">
         <v>281</v>
       </c>
       <c r="BV11" s="10" t="s">
@@ -9729,7 +9723,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="40" t="s">
         <v>169</v>
@@ -9741,7 +9735,7 @@
         <v>10</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J12" s="51" t="s">
         <v>169</v>
@@ -9753,7 +9747,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N12" s="51" t="s">
         <v>169</v>
@@ -9765,7 +9759,7 @@
         <v>10</v>
       </c>
       <c r="Q12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R12" s="51" t="s">
         <v>169</v>
@@ -9777,7 +9771,7 @@
         <v>10</v>
       </c>
       <c r="U12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V12" s="44" t="s">
         <v>171</v>
@@ -9789,7 +9783,7 @@
         <v>10</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z12" s="44" t="s">
         <v>171</v>
@@ -9801,7 +9795,7 @@
         <v>10</v>
       </c>
       <c r="AC12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD12" s="44" t="s">
         <v>171</v>
@@ -9813,7 +9807,7 @@
         <v>10</v>
       </c>
       <c r="AG12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AH12" s="44" t="s">
         <v>171</v>
@@ -9825,7 +9819,7 @@
         <v>10</v>
       </c>
       <c r="AK12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL12" s="44" t="s">
         <v>171</v>
@@ -9837,7 +9831,7 @@
         <v>10</v>
       </c>
       <c r="AO12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP12" s="44" t="s">
         <v>171</v>
@@ -9849,7 +9843,7 @@
         <v>10</v>
       </c>
       <c r="AS12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AT12" s="40" t="s">
         <v>338</v>
@@ -9861,7 +9855,7 @@
         <v>15</v>
       </c>
       <c r="AW12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AX12" s="47" t="s">
         <v>172</v>
@@ -9872,8 +9866,8 @@
       <c r="AZ12" s="49">
         <v>20</v>
       </c>
-      <c r="BA12" s="50" t="s">
-        <v>40</v>
+      <c r="BA12" s="43" t="s">
+        <v>39</v>
       </c>
       <c r="BB12" s="40" t="s">
         <v>279</v>
@@ -9895,7 +9889,7 @@
         <v>5</v>
       </c>
       <c r="BI12" s="122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BJ12" s="130" t="s">
         <v>35</v>
@@ -9907,7 +9901,7 @@
         <v>5</v>
       </c>
       <c r="BM12" s="131" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BN12" s="40" t="s">
         <v>279</v>
@@ -9916,7 +9910,7 @@
         <v>279</v>
       </c>
       <c r="BP12" s="42"/>
-      <c r="BQ12" s="174" t="s">
+      <c r="BQ12" s="173" t="s">
         <v>281</v>
       </c>
       <c r="BR12" s="44" t="s">
@@ -9926,7 +9920,7 @@
         <v>279</v>
       </c>
       <c r="BT12" s="42"/>
-      <c r="BU12" s="172" t="s">
+      <c r="BU12" s="171" t="s">
         <v>281</v>
       </c>
       <c r="BV12" s="44" t="s">
@@ -9936,7 +9930,7 @@
         <v>279</v>
       </c>
       <c r="BX12" s="42"/>
-      <c r="BY12" s="175" t="s">
+      <c r="BY12" s="174" t="s">
         <v>281</v>
       </c>
     </row>
@@ -10014,7 +10008,7 @@
         <v>10</v>
       </c>
       <c r="Y13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z13" s="162" t="s">
         <v>175</v>
@@ -10026,7 +10020,7 @@
         <v>10</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD13" s="162" t="s">
         <v>175</v>
@@ -10038,7 +10032,7 @@
         <v>10</v>
       </c>
       <c r="AG13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AH13" s="162" t="s">
         <v>175</v>
@@ -10050,7 +10044,7 @@
         <v>10</v>
       </c>
       <c r="AK13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL13" s="162" t="s">
         <v>175</v>
@@ -10062,7 +10056,7 @@
         <v>10</v>
       </c>
       <c r="AO13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP13" s="162" t="s">
         <v>175</v>
@@ -10074,7 +10068,7 @@
         <v>10</v>
       </c>
       <c r="AS13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AT13" s="12" t="s">
         <v>279</v>
@@ -10086,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="AW13" s="15" t="s">
-        <v>38</v>
+        <v>281</v>
       </c>
       <c r="AX13" s="163" t="s">
         <v>178</v>
@@ -10097,8 +10091,8 @@
       <c r="AZ13" s="165">
         <v>20</v>
       </c>
-      <c r="BA13" s="166" t="s">
-        <v>40</v>
+      <c r="BA13" s="151" t="s">
+        <v>39</v>
       </c>
       <c r="BB13" s="24" t="s">
         <v>279</v>
@@ -10113,26 +10107,26 @@
       <c r="BF13" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="BG13" s="167" t="s">
+      <c r="BG13" s="166" t="s">
         <v>279</v>
       </c>
       <c r="BH13" s="14">
         <v>15</v>
       </c>
-      <c r="BI13" s="168" t="s">
-        <v>40</v>
-      </c>
-      <c r="BJ13" s="195" t="s">
+      <c r="BI13" s="167" t="s">
+        <v>39</v>
+      </c>
+      <c r="BJ13" s="193" t="s">
         <v>174</v>
       </c>
-      <c r="BK13" s="196" t="s">
+      <c r="BK13" s="194" t="s">
         <v>279</v>
       </c>
-      <c r="BL13" s="197">
+      <c r="BL13" s="195">
         <v>15</v>
       </c>
-      <c r="BM13" s="198" t="s">
-        <v>40</v>
+      <c r="BM13" s="155" t="s">
+        <v>39</v>
       </c>
       <c r="BN13" s="12" t="s">
         <v>279</v>
@@ -10141,7 +10135,7 @@
         <v>279</v>
       </c>
       <c r="BP13" s="14"/>
-      <c r="BQ13" s="173" t="s">
+      <c r="BQ13" s="172" t="s">
         <v>281</v>
       </c>
       <c r="BR13" s="162" t="s">
@@ -10301,7 +10295,7 @@
         <v>10</v>
       </c>
       <c r="AW14" s="56" t="s">
-        <v>281</v>
+        <v>38</v>
       </c>
       <c r="AX14" s="53" t="s">
         <v>179</v>
@@ -10335,9 +10329,9 @@
         <v>25</v>
       </c>
       <c r="BI14" s="123" t="s">
-        <v>40</v>
-      </c>
-      <c r="BJ14" s="176" t="s">
+        <v>39</v>
+      </c>
+      <c r="BJ14" s="175" t="s">
         <v>37</v>
       </c>
       <c r="BK14" s="54" t="s">
@@ -10346,8 +10340,8 @@
       <c r="BL14" s="55">
         <v>30</v>
       </c>
-      <c r="BM14" s="177" t="s">
-        <v>281</v>
+      <c r="BM14" s="176" t="s">
+        <v>39</v>
       </c>
       <c r="BN14" s="53" t="s">
         <v>279</v>
@@ -10366,7 +10360,7 @@
         <v>279</v>
       </c>
       <c r="BT14" s="55"/>
-      <c r="BU14" s="178" t="s">
+      <c r="BU14" s="177" t="s">
         <v>281</v>
       </c>
       <c r="BV14" s="57" t="s">
@@ -10376,7 +10370,7 @@
         <v>279</v>
       </c>
       <c r="BX14" s="55"/>
-      <c r="BY14" s="178" t="s">
+      <c r="BY14" s="177" t="s">
         <v>281</v>
       </c>
     </row>
@@ -18303,7 +18297,7 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3/3IEoPDqTQJHL4HJyXnZL/PrbUyeFPqgsAu2cs8M3ux64aSL5NbckTnVS06sLbNRg1xmkSbQJnyy/DGBKParg==" saltValue="lHOaN8WtcfjHoHIStTU8bg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Hq7RTYkj3rTlcZ7tnIvQLz/YPgFPM4heCU/wmeTdmwGUFBYGqZ57ZiBJJoNBAaAipF7BCfYSF4krP+qmae4yAw==" saltValue="GjSJhexv4fkVsbfdFCVEJg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18349,10 +18343,10 @@
       <c r="H3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="291" t="s">
+      <c r="I3" s="290" t="s">
         <v>283</v>
       </c>
-      <c r="J3" s="292"/>
+      <c r="J3" s="291"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -18649,7 +18643,9 @@
       <c r="G20" s="58" t="s">
         <v>281</v>
       </c>
-      <c r="H20" s="1"/>
+      <c r="H20" s="292" t="s">
+        <v>346</v>
+      </c>
       <c r="I20" s="135" t="s">
         <v>303</v>
       </c>
@@ -18667,7 +18663,7 @@
       <c r="C21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -18676,7 +18672,9 @@
       <c r="G21" t="s">
         <v>280</v>
       </c>
-      <c r="H21" s="1"/>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I21" s="135" t="s">
         <v>305</v>
       </c>
@@ -18694,13 +18692,15 @@
       <c r="C22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>11</v>
+      <c r="D22" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="I22" s="135" t="s">
         <v>66</v>
       </c>
@@ -18718,13 +18718,15 @@
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>10</v>
+      <c r="D23" s="3" t="s">
+        <v>348</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="H23" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="I23" s="132" t="s">
         <v>69</v>
       </c>
@@ -18739,8 +18741,8 @@
       <c r="C24" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>278</v>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
@@ -18757,8 +18759,8 @@
       <c r="C25" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>58</v>
+      <c r="D25" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>280</v>
@@ -18771,9 +18773,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D26" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="I26" s="132" t="s">
         <v>62</v>
       </c>
@@ -18782,9 +18782,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D27" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="D27" s="1"/>
       <c r="I27" s="135" t="s">
         <v>313</v>
       </c>
@@ -18815,7 +18813,7 @@
       <c r="C29" s="61" t="s">
         <v>232</v>
       </c>
-      <c r="D29" s="169" t="s">
+      <c r="D29" s="168" t="s">
         <v>329</v>
       </c>
       <c r="E29" s="61" t="s">
@@ -18838,7 +18836,7 @@
       <c r="C30" t="s">
         <v>233</v>
       </c>
-      <c r="D30" s="170" t="s">
+      <c r="D30" s="169" t="s">
         <v>331</v>
       </c>
       <c r="E30" s="8" t="s">
@@ -18861,7 +18859,7 @@
       <c r="C31" t="s">
         <v>234</v>
       </c>
-      <c r="D31" s="170" t="s">
+      <c r="D31" s="169" t="s">
         <v>332</v>
       </c>
       <c r="I31" s="132" t="s">
@@ -18881,7 +18879,7 @@
       <c r="C32" t="s">
         <v>235</v>
       </c>
-      <c r="D32" s="170" t="s">
+      <c r="D32" s="169" t="s">
         <v>333</v>
       </c>
       <c r="I32" s="132" t="s">
@@ -19106,7 +19104,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yHNgiZA/OCwRkhxdyfCWOugT+O0FqKaizx+MoVUUp/DQaKRjSZX/XCYHlrmhoFmgrtbnNeS2vpnJIb4CNFBl4w==" saltValue="1+Oe8inJlCfuL4gTyOBMjg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eh5K9m6O6smEA5cja9iXACCfrggf0YAxvTvZkCoDPqLSaCqSwBKgW/C7i5UWlMEosPzrhxFY/amioBzHt3R1vQ==" saltValue="brPAxXGAMl9gVhXHC3rDIg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
@@ -19115,36 +19113,41 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A21:A23">
+    <cfRule type="expression" priority="6">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:D9">
+    <cfRule type="expression" priority="7">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:G5 E6:G12">
+    <cfRule type="expression" priority="8">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30:I33">
+    <cfRule type="expression" priority="3">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
+    <cfRule type="expression" priority="4">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23:J29">
     <cfRule type="expression" priority="5">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D9">
-    <cfRule type="expression" priority="6">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:G5 E6:G12">
-    <cfRule type="expression" priority="7">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I30:I33">
+  <conditionalFormatting sqref="J31:J33">
     <cfRule type="expression" priority="2">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
-    <cfRule type="expression" priority="3">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I23:J29">
-    <cfRule type="expression" priority="4">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J33">
+  <conditionalFormatting sqref="H21:H22">
     <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
@@ -19155,21 +19158,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -19372,24 +19360,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19406,4 +19392,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/AutosurveillanceTemplates/PREL.xlsx
+++ b/AutosurveillanceTemplates/PREL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C79A2F-DCCB-41FC-B861-38AAE9FDA241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6BEC83-9B9D-4294-BB5E-35B2536F4D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,8 +60,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="349">
   <si>
     <t>Code</t>
   </si>
@@ -1947,7 +1969,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode=";;;"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2149,13 +2171,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3718,7 +3733,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="294">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4031,7 +4046,7 @@
     <xf numFmtId="0" fontId="26" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4243,7 +4258,7 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4255,7 +4270,7 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4264,13 +4279,13 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4294,11 +4309,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="26" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4324,13 +4339,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4382,10 +4397,10 @@
     <xf numFmtId="0" fontId="29" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4437,10 +4452,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4484,7 +4499,7 @@
     <xf numFmtId="165" fontId="26" fillId="13" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4511,13 +4526,16 @@
     <xf numFmtId="164" fontId="26" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4586,13 +4604,13 @@
     <xf numFmtId="0" fontId="29" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4604,14 +4622,14 @@
     <xf numFmtId="1" fontId="26" fillId="13" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5209,7 +5227,8 @@
     <col min="19" max="19" width="2.703125" style="80" customWidth="1"/>
     <col min="20" max="20" width="2.703125" style="196" customWidth="1"/>
     <col min="21" max="26" width="10.703125" style="196"/>
-    <col min="27" max="30" width="10.703125" style="197"/>
+    <col min="27" max="29" width="10.703125" style="293"/>
+    <col min="30" max="30" width="10.703125" style="196"/>
     <col min="31" max="16384" width="10.703125" style="80"/>
   </cols>
   <sheetData>
@@ -5235,24 +5254,24 @@
     </row>
     <row r="2" spans="2:21" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="66"/>
-      <c r="C2" s="267" t="s">
+      <c r="C2" s="268" t="s">
         <v>282</v>
       </c>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="268"/>
-      <c r="P2" s="268"/>
-      <c r="Q2" s="268"/>
-      <c r="R2" s="269"/>
+      <c r="D2" s="269"/>
+      <c r="E2" s="269"/>
+      <c r="F2" s="269"/>
+      <c r="G2" s="269"/>
+      <c r="H2" s="269"/>
+      <c r="I2" s="269"/>
+      <c r="J2" s="269"/>
+      <c r="K2" s="269"/>
+      <c r="L2" s="269"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="269"/>
+      <c r="Q2" s="269"/>
+      <c r="R2" s="270"/>
       <c r="S2" s="67"/>
     </row>
     <row r="3" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -5268,17 +5287,17 @@
         <v>242</v>
       </c>
       <c r="I3" s="263"/>
-      <c r="J3" s="264"/>
-      <c r="K3" s="264"/>
-      <c r="L3" s="264"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
       <c r="M3" s="263" t="s">
         <v>244</v>
       </c>
       <c r="N3" s="263"/>
       <c r="O3" s="263"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="266"/>
+      <c r="P3" s="266"/>
+      <c r="Q3" s="266"/>
+      <c r="R3" s="267"/>
       <c r="S3" s="79"/>
     </row>
     <row r="4" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -5294,17 +5313,17 @@
         <v>249</v>
       </c>
       <c r="I4" s="263"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
       <c r="M4" s="263" t="s">
         <v>245</v>
       </c>
       <c r="N4" s="263"/>
       <c r="O4" s="263"/>
-      <c r="P4" s="265"/>
-      <c r="Q4" s="265"/>
-      <c r="R4" s="266"/>
+      <c r="P4" s="266"/>
+      <c r="Q4" s="266"/>
+      <c r="R4" s="267"/>
       <c r="S4" s="79"/>
     </row>
     <row r="5" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -5320,17 +5339,17 @@
         <v>248</v>
       </c>
       <c r="I5" s="263"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
+      <c r="J5" s="265"/>
+      <c r="K5" s="265"/>
+      <c r="L5" s="265"/>
       <c r="M5" s="263" t="s">
         <v>246</v>
       </c>
       <c r="N5" s="263"/>
       <c r="O5" s="263"/>
-      <c r="P5" s="273"/>
-      <c r="Q5" s="273"/>
-      <c r="R5" s="274"/>
+      <c r="P5" s="274"/>
+      <c r="Q5" s="274"/>
+      <c r="R5" s="275"/>
       <c r="S5" s="79"/>
     </row>
     <row r="6" spans="2:21" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -5346,9 +5365,9 @@
         <v>243</v>
       </c>
       <c r="I6" s="240"/>
-      <c r="J6" s="241" t="str">
+      <c r="J6" s="241">
         <f>D37</f>
-        <v>Vanne de prélèvement asservie</v>
+        <v>0</v>
       </c>
       <c r="K6" s="241"/>
       <c r="L6" s="241"/>
@@ -5454,17 +5473,17 @@
       </c>
       <c r="E11" s="246"/>
       <c r="F11" s="247"/>
-      <c r="G11" s="270"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="271"/>
-      <c r="L11" s="271"/>
-      <c r="M11" s="271"/>
-      <c r="N11" s="271"/>
-      <c r="O11" s="271"/>
-      <c r="P11" s="271"/>
-      <c r="Q11" s="272"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="272"/>
+      <c r="I11" s="272"/>
+      <c r="J11" s="272"/>
+      <c r="K11" s="272"/>
+      <c r="L11" s="272"/>
+      <c r="M11" s="272"/>
+      <c r="N11" s="272"/>
+      <c r="O11" s="272"/>
+      <c r="P11" s="272"/>
+      <c r="Q11" s="273"/>
       <c r="R11" s="95"/>
       <c r="S11" s="71"/>
     </row>
@@ -5647,16 +5666,16 @@
     <row r="19" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="69"/>
       <c r="C19" s="94"/>
-      <c r="D19" s="277"/>
-      <c r="E19" s="278"/>
+      <c r="D19" s="278"/>
+      <c r="E19" s="279"/>
       <c r="F19" s="114"/>
       <c r="G19" s="115"/>
       <c r="H19" s="116"/>
-      <c r="I19" s="275" t="str">
+      <c r="I19" s="276" t="str">
         <f>IF(F19&lt;&gt;"",AVERAGE(F19:H19),"")</f>
         <v/>
       </c>
-      <c r="J19" s="276"/>
+      <c r="J19" s="277"/>
       <c r="K19" s="107" t="str">
         <f>IF(COUNTA(F19:H19)&gt;0,STDEVP(F19:H19),"")</f>
         <v/>
@@ -5712,14 +5731,14 @@
       </c>
       <c r="J21" s="224"/>
       <c r="K21" s="81"/>
-      <c r="L21" s="281" t="s">
+      <c r="L21" s="282" t="s">
         <v>214</v>
       </c>
-      <c r="M21" s="282"/>
-      <c r="N21" s="282"/>
-      <c r="O21" s="282"/>
-      <c r="P21" s="282"/>
-      <c r="Q21" s="283"/>
+      <c r="M21" s="283"/>
+      <c r="N21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="283"/>
+      <c r="Q21" s="284"/>
       <c r="R21" s="95"/>
       <c r="S21" s="71"/>
     </row>
@@ -5742,14 +5761,14 @@
       </c>
       <c r="J22" s="254"/>
       <c r="K22" s="81"/>
-      <c r="L22" s="284" t="s">
+      <c r="L22" s="285" t="s">
         <v>238</v>
       </c>
-      <c r="M22" s="285"/>
-      <c r="N22" s="285"/>
-      <c r="O22" s="285"/>
-      <c r="P22" s="285"/>
-      <c r="Q22" s="286"/>
+      <c r="M22" s="286"/>
+      <c r="N22" s="286"/>
+      <c r="O22" s="286"/>
+      <c r="P22" s="286"/>
+      <c r="Q22" s="287"/>
       <c r="R22" s="95"/>
       <c r="S22" s="71"/>
     </row>
@@ -5769,13 +5788,13 @@
       </c>
       <c r="J23" s="261"/>
       <c r="K23" s="81"/>
-      <c r="L23" s="279" t="s">
+      <c r="L23" s="280" t="s">
         <v>256</v>
       </c>
-      <c r="M23" s="279"/>
-      <c r="N23" s="279"/>
-      <c r="O23" s="279"/>
-      <c r="P23" s="280"/>
+      <c r="M23" s="280"/>
+      <c r="N23" s="280"/>
+      <c r="O23" s="280"/>
+      <c r="P23" s="281"/>
       <c r="Q23" s="121"/>
       <c r="R23" s="95"/>
       <c r="S23" s="71"/>
@@ -5805,13 +5824,13 @@
       </c>
       <c r="J24" s="231"/>
       <c r="K24" s="81"/>
-      <c r="L24" s="279" t="s">
+      <c r="L24" s="280" t="s">
         <v>257</v>
       </c>
-      <c r="M24" s="279"/>
-      <c r="N24" s="279"/>
-      <c r="O24" s="279"/>
-      <c r="P24" s="280"/>
+      <c r="M24" s="280"/>
+      <c r="N24" s="280"/>
+      <c r="O24" s="280"/>
+      <c r="P24" s="281"/>
       <c r="Q24" s="121"/>
       <c r="R24" s="95"/>
       <c r="S24" s="71"/>
@@ -5831,13 +5850,13 @@
       <c r="I25" s="81"/>
       <c r="J25" s="81"/>
       <c r="K25" s="81"/>
-      <c r="L25" s="279" t="s">
+      <c r="L25" s="280" t="s">
         <v>258</v>
       </c>
-      <c r="M25" s="279"/>
-      <c r="N25" s="279"/>
-      <c r="O25" s="279"/>
-      <c r="P25" s="280"/>
+      <c r="M25" s="280"/>
+      <c r="N25" s="280"/>
+      <c r="O25" s="280"/>
+      <c r="P25" s="281"/>
       <c r="Q25" s="108" t="str">
         <f>IF(COUNTA(Q23:Q24)&gt;0,TRUNC(Q24/Q23,0),"")</f>
         <v/>
@@ -5858,13 +5877,13 @@
       <c r="I26" s="222"/>
       <c r="J26" s="76"/>
       <c r="K26" s="81"/>
-      <c r="L26" s="279" t="s">
+      <c r="L26" s="280" t="s">
         <v>259</v>
       </c>
-      <c r="M26" s="279"/>
-      <c r="N26" s="279"/>
-      <c r="O26" s="279"/>
-      <c r="P26" s="280"/>
+      <c r="M26" s="280"/>
+      <c r="N26" s="280"/>
+      <c r="O26" s="280"/>
+      <c r="P26" s="281"/>
       <c r="Q26" s="120"/>
       <c r="R26" s="95"/>
       <c r="S26" s="71"/>
@@ -5886,13 +5905,13 @@
       <c r="I27" s="226"/>
       <c r="J27" s="81"/>
       <c r="K27" s="81"/>
-      <c r="L27" s="279" t="s">
+      <c r="L27" s="280" t="s">
         <v>255</v>
       </c>
-      <c r="M27" s="279"/>
-      <c r="N27" s="279"/>
-      <c r="O27" s="279"/>
-      <c r="P27" s="280"/>
+      <c r="M27" s="280"/>
+      <c r="N27" s="280"/>
+      <c r="O27" s="280"/>
+      <c r="P27" s="281"/>
       <c r="Q27" s="119"/>
       <c r="R27" s="95"/>
       <c r="S27" s="71"/>
@@ -5902,11 +5921,11 @@
       <c r="C28" s="94"/>
       <c r="D28" s="213"/>
       <c r="E28" s="213"/>
-      <c r="F28" s="289" t="str">
+      <c r="F28" s="290" t="str">
         <f>IF(AND(I19&lt;&gt;"", Q25&lt;&gt;""),(I19*Q25),"")</f>
         <v/>
       </c>
-      <c r="G28" s="289"/>
+      <c r="G28" s="290"/>
       <c r="H28" s="227" t="str">
         <f>IF(AND(D28&gt;0,F28),(D28-F28)/F28,"")</f>
         <v/>
@@ -5914,13 +5933,13 @@
       <c r="I28" s="227"/>
       <c r="J28" s="81"/>
       <c r="K28" s="81"/>
-      <c r="L28" s="287" t="s">
+      <c r="L28" s="288" t="s">
         <v>215</v>
       </c>
-      <c r="M28" s="287"/>
-      <c r="N28" s="287"/>
-      <c r="O28" s="287"/>
-      <c r="P28" s="288"/>
+      <c r="M28" s="288"/>
+      <c r="N28" s="288"/>
+      <c r="O28" s="288"/>
+      <c r="P28" s="289"/>
       <c r="Q28" s="108" t="str">
         <f>IF(AND(Q26&lt;&gt;"",Q25&lt;&gt;""),Q25/(Q26/3600),"")</f>
         <v/>
@@ -6137,9 +6156,7 @@
     <row r="37" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="69"/>
       <c r="C37" s="94"/>
-      <c r="D37" s="217" t="s">
-        <v>21</v>
-      </c>
+      <c r="D37" s="217"/>
       <c r="E37" s="217"/>
       <c r="F37" s="217"/>
       <c r="G37" s="217"/>
@@ -6197,7 +6214,7 @@
       </c>
       <c r="E39" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D39+2,FALSE),"-")</f>
-        <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
+        <v>-</v>
       </c>
       <c r="F39" s="209"/>
       <c r="G39" s="209"/>
@@ -6205,7 +6222,7 @@
       <c r="I39" s="210"/>
       <c r="J39" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D39+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D39+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>En cas d'accès nécessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
+        <v/>
       </c>
       <c r="K39" s="209"/>
       <c r="L39" s="209"/>
@@ -6216,14 +6233,15 @@
         <f>IF(OR(N39 = "Validé",N39="Réserve",N39="Oui"),Q39,0)</f>
         <v>0</v>
       </c>
-      <c r="Q39" s="83">
+      <c r="Q39" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D39+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="R39" s="95"/>
       <c r="S39" s="71"/>
-      <c r="U39" s="196" t="s">
-        <v>39</v>
+      <c r="U39" s="196" t="str" cm="1">
+        <f t="array" ref="U39">IFERROR(INDEX(Critères!$B$3:$BZ$16, D39+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="40" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6234,7 +6252,7 @@
       </c>
       <c r="E40" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D40+2,FALSE),"-")</f>
-        <v>Le point de prélèvement est-il correctement implanté ?</v>
+        <v>-</v>
       </c>
       <c r="F40" s="209"/>
       <c r="G40" s="209"/>
@@ -6253,14 +6271,15 @@
         <f t="shared" ref="P40:P48" si="0">IF(OR(N40 = "Validé",N40="Réserve",N40="Oui"),Q40,0)</f>
         <v>0</v>
       </c>
-      <c r="Q40" s="83">
+      <c r="Q40" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D40+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="R40" s="95"/>
       <c r="S40" s="71"/>
-      <c r="U40" s="196" t="s">
-        <v>39</v>
+      <c r="U40" s="196" t="str" cm="1">
+        <f t="array" ref="U40">IFERROR(INDEX(Critères!$B$3:$BZ$16, D40+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="41" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6271,7 +6290,7 @@
       </c>
       <c r="E41" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D41+2,FALSE),"-")</f>
-        <v>La propreté et l'état d'entretien du dispositif de prélèvement sont-ils satisfaisants ?</v>
+        <v>-</v>
       </c>
       <c r="F41" s="209"/>
       <c r="G41" s="209"/>
@@ -6279,8 +6298,7 @@
       <c r="I41" s="210"/>
       <c r="J41" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D41+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D41+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité du prélèvement doit entrainer un jugement à "Non Validé".
-Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité du prélèvement doit avoir un jugement "Validé avec réserve".</v>
+        <v/>
       </c>
       <c r="K41" s="209"/>
       <c r="L41" s="209"/>
@@ -6291,14 +6309,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="83">
+      <c r="Q41" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D41+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="R41" s="95"/>
       <c r="S41" s="71"/>
-      <c r="U41" s="196" t="s">
-        <v>39</v>
+      <c r="U41" s="196" t="str" cm="1">
+        <f t="array" ref="U41">IFERROR(INDEX(Critères!$B$3:$BZ$16, D41+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="42" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6309,7 +6328,7 @@
       </c>
       <c r="E42" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D42+2,FALSE),"-")</f>
-        <v>Le dispositif de prélèvement présente t-il un état de fonctionnement satisfaisant, son diamètre est-il ≥ à 9 mm ?</v>
+        <v>-</v>
       </c>
       <c r="F42" s="209"/>
       <c r="G42" s="209"/>
@@ -6324,21 +6343,22 @@
       <c r="M42" s="210"/>
       <c r="N42" s="211" t="str">
         <f>IF(E42="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U14,"Non contrôlé"))</f>
-        <v>Non contrôlé</v>
+        <v>Non applicable</v>
       </c>
       <c r="O42" s="212"/>
       <c r="P42" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q42" s="83">
+      <c r="Q42" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="R42" s="95"/>
       <c r="S42" s="71"/>
-      <c r="U42" s="196" t="s">
-        <v>39</v>
+      <c r="U42" s="196" t="str" cm="1">
+        <f t="array" ref="U42">IFERROR(INDEX(Critères!$B$3:$BZ$16, D42+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="43" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6349,7 +6369,7 @@
       </c>
       <c r="E43" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D43+2,FALSE),"-")</f>
-        <v>Le volume de prélèvement par cycle est-il ≥ à 50 ml et est-il répétable à ± 5 % ?</v>
+        <v>-</v>
       </c>
       <c r="F43" s="209"/>
       <c r="G43" s="209"/>
@@ -6357,28 +6377,29 @@
       <c r="I43" s="210"/>
       <c r="J43" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>Contrôle à réaliser sur 3 prélèvements</v>
+        <v/>
       </c>
       <c r="K43" s="209"/>
       <c r="L43" s="209"/>
       <c r="M43" s="210"/>
       <c r="N43" s="211" t="str">
         <f>IF(E43="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U19,"Non contrôlé"))</f>
-        <v>Non contrôlé</v>
+        <v>Non applicable</v>
       </c>
       <c r="O43" s="212"/>
       <c r="P43" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="83">
+      <c r="Q43" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="R43" s="95"/>
       <c r="S43" s="71"/>
-      <c r="U43" s="196" t="s">
-        <v>40</v>
+      <c r="U43" s="196" t="str" cm="1">
+        <f t="array" ref="U43">IFERROR(INDEX(Critères!$B$3:$BZ$16, D43+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="44" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6397,7 +6418,7 @@
       <c r="I44" s="210"/>
       <c r="J44" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>question non applicable</v>
+        <v/>
       </c>
       <c r="K44" s="209"/>
       <c r="L44" s="209"/>
@@ -6411,14 +6432,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="83">
+      <c r="Q44" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R44" s="95"/>
       <c r="S44" s="71"/>
-      <c r="U44" s="196" t="s">
-        <v>40</v>
+      <c r="U44" s="196" t="str" cm="1">
+        <f t="array" ref="U44">IFERROR(INDEX(Critères!$B$3:$BZ$16, D44+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="45" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6429,7 +6451,7 @@
       </c>
       <c r="E45" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D45+2,FALSE),"-")</f>
-        <v>La vanne de prélèvement est-elle asservie au débit, ou au volume écoulé, et assure-t-elle un nombre de prélèvements égal, en moyenne, à au moins à 6 par heure de rejet effectif ? soit 144 prélèvements unitaires par 24h de rejet.</v>
+        <v>-</v>
       </c>
       <c r="F45" s="209"/>
       <c r="G45" s="209"/>
@@ -6437,28 +6459,29 @@
       <c r="I45" s="210"/>
       <c r="J45" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>Tolérance de validation à 4 prélèvements par heure de rejet (soit 96 prélèvements/jour), sur justification d'un évènement exceptionnel.</v>
+        <v/>
       </c>
       <c r="K45" s="209"/>
       <c r="L45" s="209"/>
       <c r="M45" s="210"/>
       <c r="N45" s="211" t="str">
         <f>IF(E45="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),V28,"Non contrôlé"))</f>
-        <v>Non contrôlé</v>
+        <v>Non applicable</v>
       </c>
       <c r="O45" s="212"/>
       <c r="P45" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q45" s="83">
+      <c r="Q45" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="R45" s="95"/>
       <c r="S45" s="71"/>
-      <c r="U45" s="196" t="s">
-        <v>39</v>
+      <c r="U45" s="196" t="str" cm="1">
+        <f t="array" ref="U45">IFERROR(INDEX(Critères!$B$3:$BZ$16, D45+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="46" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6469,7 +6492,7 @@
       </c>
       <c r="E46" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D46+2,FALSE),"-")</f>
-        <v xml:space="preserve"> Les horaires de prélèvement et de totalisation des débits sont-ils synchronisés ?</v>
+        <v>-</v>
       </c>
       <c r="F46" s="209"/>
       <c r="G46" s="209"/>
@@ -6477,28 +6500,29 @@
       <c r="I46" s="210"/>
       <c r="J46" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="K46" s="209"/>
       <c r="L46" s="209"/>
       <c r="M46" s="210"/>
       <c r="N46" s="211" t="str">
         <f>IF(E46="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),V28,"Non contrôlé"))</f>
-        <v>Non contrôlé</v>
+        <v>Non applicable</v>
       </c>
       <c r="O46" s="212"/>
       <c r="P46" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q46" s="83">
+      <c r="Q46" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="R46" s="95"/>
       <c r="S46" s="71"/>
-      <c r="U46" s="196" t="s">
-        <v>40</v>
+      <c r="U46" s="196" t="str" cm="1">
+        <f t="array" ref="U46">IFERROR(INDEX(Critères!$B$3:$BZ$16, D46+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="47" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6509,7 +6533,7 @@
       </c>
       <c r="E47" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D47+2,FALSE),"-")</f>
-        <v>La température de l'enceinte de prélèvement est-elle adaptée? Si elle est réfrigérée, sa température est-elle maîtrisée à 5°C ± 3°C ?</v>
+        <v>-</v>
       </c>
       <c r="F47" s="209"/>
       <c r="G47" s="209"/>
@@ -6517,28 +6541,29 @@
       <c r="I47" s="210"/>
       <c r="J47" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="K47" s="209"/>
       <c r="L47" s="209"/>
       <c r="M47" s="210"/>
       <c r="N47" s="211" t="str">
         <f>IF(E47="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U32,"Non contrôlé"))</f>
-        <v>Non contrôlé</v>
+        <v>Non applicable</v>
       </c>
       <c r="O47" s="212"/>
       <c r="P47" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="83">
+      <c r="Q47" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="R47" s="95"/>
       <c r="S47" s="71"/>
-      <c r="U47" s="196" t="s">
-        <v>40</v>
+      <c r="U47" s="196" t="str" cm="1">
+        <f t="array" ref="U47">IFERROR(INDEX(Critères!$B$3:$BZ$16, D47+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="48" spans="2:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6549,7 +6574,7 @@
       </c>
       <c r="E48" s="208" t="str">
         <f>IFERROR(HLOOKUP($D$37,Critères!$B$3:$BY$16,D48+2,FALSE),"-")</f>
-        <v>L'écart entre le volume théorique et le volume prélevé est-il ≤ à 10% ?</v>
+        <v>-</v>
       </c>
       <c r="F48" s="209"/>
       <c r="G48" s="209"/>
@@ -6557,28 +6582,29 @@
       <c r="I48" s="210"/>
       <c r="J48" s="208" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="K48" s="209"/>
       <c r="L48" s="209"/>
       <c r="M48" s="210"/>
       <c r="N48" s="211" t="str">
         <f>IF(E48="-","Non applicable",IF(OR($D$37=Critères!BF3,$D$37=Critères!BJ3),U28,"Non contrôlé"))</f>
-        <v>Non contrôlé</v>
+        <v>Non applicable</v>
       </c>
       <c r="O48" s="212"/>
       <c r="P48" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="83">
+      <c r="Q48" s="83" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$37, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R48" s="95"/>
       <c r="S48" s="71"/>
-      <c r="U48" s="196" t="s">
-        <v>40</v>
+      <c r="U48" s="196" t="str" cm="1">
+        <f t="array" ref="U48">IFERROR(INDEX(Critères!$B$3:$BZ$16, D48+2, MATCH($D$37, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v/>
       </c>
     </row>
     <row r="49" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6816,7 +6842,7 @@
       <c r="S59" s="75"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="miuWYHEJEH83k18AURW2vDLzCwXzZQS+VdMHxK9uE+HO7zVGxUCBxB/+ZU8sbtGikoWJD87bW71RvYTRjGYghw==" saltValue="W41jshMzvoeNNF5b4T1QlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hgphlmU4B+p6mhvA28+N9M40P6//pi6AFc7WTHT1IGeH++nzrolk2S+Tupt0fIcUd2/vVDwO7tJBGAhsBoAu+Q==" saltValue="oStN6KK9im1YODWpJGCwfQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="131">
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="D19:E19"/>
@@ -18297,7 +18323,7 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Hq7RTYkj3rTlcZ7tnIvQLz/YPgFPM4heCU/wmeTdmwGUFBYGqZ57ZiBJJoNBAaAipF7BCfYSF4krP+qmae4yAw==" saltValue="GjSJhexv4fkVsbfdFCVEJg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Cb8aoPiOnWXsxsHOqzrbg4PIt8NA5eu2cKvs7RZ2RDxL5F1ZxZfvBO32BM4BxAPoqae6FAB9pvVTS040uV5OVA==" saltValue="Id9Bfmd3+mJY2I0zhzu0Kg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18343,10 +18369,10 @@
       <c r="H3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="290" t="s">
+      <c r="I3" s="291" t="s">
         <v>283</v>
       </c>
-      <c r="J3" s="291"/>
+      <c r="J3" s="292"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -18643,7 +18669,7 @@
       <c r="G20" s="58" t="s">
         <v>281</v>
       </c>
-      <c r="H20" s="292" t="s">
+      <c r="H20" s="197" t="s">
         <v>346</v>
       </c>
       <c r="I20" s="135" t="s">
@@ -19104,7 +19130,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eh5K9m6O6smEA5cja9iXACCfrggf0YAxvTvZkCoDPqLSaCqSwBKgW/C7i5UWlMEosPzrhxFY/amioBzHt3R1vQ==" saltValue="brPAxXGAMl9gVhXHC3rDIg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8vGisOE1Ry8c5+Y2+78zRrXnSc9H0ZXa07elVzqd2zeoWW1P9tCTblqDtdNUQ4k9+6kA8Is7ffV+ai47viK7Qg==" saltValue="fxX0x7xSwWDXSqlQWZz0Sw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
@@ -19124,6 +19150,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:G5 E6:G12">
     <cfRule type="expression" priority="8">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:H22">
+    <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19147,17 +19178,18 @@
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H22">
-    <cfRule type="expression" priority="1">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -19360,7 +19392,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -19369,13 +19401,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19394,19 +19429,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>